--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -172,14 +172,14 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -318,12 +318,252 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$17</f>
+              <f>'ベンチプレス'!$A$130:$A$139</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$17</f>
+              <f>'ベンチプレス'!$C$130:$C$139</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>週</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>推定1RM (kg)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>デッドリフト 推定1RM 推移</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>デッドリフト 推定1RM</v>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'デッドリフト'!$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'デッドリフト'!$C$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>週</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>推定1RM (kg)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>スクワット 推定1RM 推移</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>スクワット 推定1RM</v>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'スクワット'!$A$45:$A$50</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'スクワット'!$C$45:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -398,7 +638,61 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
+      <row>127</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
       <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -708,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -724,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-05-13）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-05-18）</t>
         </is>
       </c>
     </row>
@@ -758,10 +1052,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>95</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -776,14 +1070,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
@@ -794,14 +1088,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -857,21 +1151,229 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>95</v>
+        <v>85.2</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>2350</v>
+        <v>1560</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>2350</v>
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="9" t="n">
+        <v>6122.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>5355</v>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>1070</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>6425</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>5967.2</v>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="9" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>2132.5</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>8099.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>550</v>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="11" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>2540</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>3980</v>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="9" t="n">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>3545</v>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>6835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="9" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>4670</v>
       </c>
     </row>
   </sheetData>
@@ -884,6 +1386,3905 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ベンチプレス  詳細ログ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>種目名</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>重量 (kg)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>回数</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ボリューム</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>310</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>525</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>375</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>507.5</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>580</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>435</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>560</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>270</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>72.59999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G50" s="11" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G54" s="11" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>520</v>
+      </c>
+      <c r="G56" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>455</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>76.40000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="G58" s="11" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>325</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>73.09999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>73.09999999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>76.90000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G64" s="11" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="G66" s="11" t="n">
+        <v>73.40000000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G68" s="11" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="G70" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G72" s="11" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G74" s="11" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G76" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G77" s="9" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="G78" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="G80" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G81" s="9" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G84" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="G85" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G86" s="11" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G88" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>345</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>460</v>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>345</v>
+      </c>
+      <c r="G92" s="11" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="G93" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G94" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>440</v>
+      </c>
+      <c r="G97" s="9" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="G98" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>275</v>
+      </c>
+      <c r="G99" s="9" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G100" s="11" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" s="9" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G102" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G103" s="9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G104" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G105" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G106" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="G107" s="9" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="G108" s="11" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G110" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G112" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="G113" s="9" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="G114" s="11" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="G116" s="11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>420</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="G118" s="11" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G120" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="G121" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G122" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G124" s="11" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G126" s="11" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>3545</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>3980</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>5967.2</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>5355</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -903,9 +5304,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ベンチプレス  詳細ログ</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>デッドリフト  詳細ログ</t>
         </is>
       </c>
     </row>
@@ -947,181 +5348,123 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>ベンチプレス　（バーベル）</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>26.7</v>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>87.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>ベンチプレス　（バーベル）</t>
+          <t>Deadlift (Barbell)</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>58.3</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>ベンチプレス　（バーベル）</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>325</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>75.8</v>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>87.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>ベンチプレス　（バーベル）</t>
+          <t>Deadlift (Barbell)</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>ベンチプレス　（バーベル）</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>525</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>92.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>ベンチプレス　（バーベル）</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>450</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>週別集計</t>
         </is>
@@ -1162,23 +5505,23 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2350</v>
+        <v>1120</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1191,124 +5534,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>デッドリフト  詳細ログ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>種目名</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>重量 (kg)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>回数</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>ボリューム</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1365,50 +5597,1285 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>スクワット　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>スクワット　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>スクワット　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>スクワット　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>スクワット　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>225</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>375</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>435</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>85.59999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>520</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>520</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Squat (Barbell)</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>週別集計</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>最大重量 (kg)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>推定1RM (kg)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>総Volume (kg)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>セッション数</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>セット数</t>
         </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>2132.5</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$130:$A$139</f>
+              <f>'ベンチプレス'!$A$137:$A$146</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$130:$C$139</f>
+              <f>'ベンチプレス'!$C$137:$C$146</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-05-18）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-05-25）</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1052,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>80</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>85.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1560</v>
+        <v>4060</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>1560</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="11">
@@ -1391,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1451,7 +1451,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1480,7 +1480,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1555,19 +1555,19 @@
         <v>77.5</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>310</v>
+        <v>542.5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>85.2</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1584,19 +1584,19 @@
         <v>77.5</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>81.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1609,231 +1609,231 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>60</v>
+      <c r="D9" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>465</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>67.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>20</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>232.5</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>25</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>57.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>525</v>
+        <v>195</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>450</v>
+        <v>4</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>310</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>86.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>375</v>
+        <v>2</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>155</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>84.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>25</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1842,27 +1842,27 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1871,27 +1871,27 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>300</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>67.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1900,27 +1900,27 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>71.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1928,28 +1928,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>72.5</v>
+      <c r="D20" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>507.5</v>
+      <c r="F20" s="10" t="n">
+        <v>525</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>85.2</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1957,28 +1957,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>72.5</v>
+      <c r="D21" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>580</v>
+        <v>6</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>450</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>87</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -1986,17 +1986,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>72.5</v>
+      <c r="D22" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>435</v>
+        <v>5</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>375</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>83.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2015,23 +2015,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>62.5</v>
+      <c r="D23" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>750</v>
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>81.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -2045,22 +2045,22 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2074,22 +2074,22 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>60</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>64.5</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2131,23 +2131,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
-        <v>70</v>
+      <c r="D27" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>560</v>
+        <v>7</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>84</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2160,23 +2160,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>70</v>
+      <c r="D28" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>560</v>
+      <c r="F28" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2189,23 +2189,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
-        <v>70</v>
+      <c r="D29" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>420</v>
+      <c r="F29" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>80.5</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -2218,17 +2218,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>80</v>
+      <c r="D30" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>80</v>
+        <v>12</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>82</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="31">
@@ -2248,27 +2248,27 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2277,27 +2277,27 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2306,27 +2306,27 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>50</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2335,27 +2335,27 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>58.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -2364,27 +2364,27 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>61.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2393,27 +2393,27 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>65</v>
+        <v>420</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>66.59999999999999</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -2422,27 +2422,27 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>78.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>80.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
@@ -2480,16 +2480,16 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>75.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
@@ -2509,16 +2509,16 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
@@ -2541,19 +2541,19 @@
         <v>50</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>57.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -2567,22 +2567,22 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>25</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>48</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -2625,22 +2625,22 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>57.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -2654,22 +2654,22 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>61.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2682,23 +2682,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>67.5</v>
+      <c r="D46" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>337.5</v>
+        <v>3</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>210</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2711,23 +2711,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>67.5</v>
+      <c r="D47" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>472.5</v>
+        <v>4</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>79.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2740,17 +2740,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n">
-        <v>67.5</v>
+      <c r="D48" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>270</v>
+        <v>6</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>74.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="49">
@@ -2769,17 +2769,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>67.5</v>
+      <c r="D49" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>202.5</v>
+        <v>10</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>72.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2798,17 +2798,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
-        <v>77.5</v>
+      <c r="D50" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>77.5</v>
+        <v>8</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>79.40000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51">
@@ -2828,27 +2828,27 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>72</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -2857,27 +2857,27 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>25</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2885,28 +2885,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
-        <v>40</v>
+      <c r="D53" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>400</v>
+        <v>5</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>337.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>50</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -2914,28 +2914,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n">
-        <v>50</v>
+      <c r="D54" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" s="10" t="n">
-        <v>250</v>
+        <v>7</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>56.2</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2943,28 +2943,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
-        <v>65</v>
+      <c r="D55" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>195</v>
+        <v>4</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -2972,28 +2972,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n">
-        <v>65</v>
+      <c r="D56" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>520</v>
+        <v>3</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>78</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -3001,28 +3001,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
-        <v>65</v>
+      <c r="D57" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>455</v>
+        <v>1</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>76.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3031,16 +3031,16 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>195</v>
+        <v>480</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59">
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
@@ -3089,16 +3089,16 @@
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -3118,22 +3118,22 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>35</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3176,22 +3176,22 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3205,22 +3205,22 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>53.8</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3233,23 +3233,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D65" s="9" t="n">
-        <v>62.5</v>
+      <c r="D65" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>500</v>
+        <v>3</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>195</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>75</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3262,23 +3262,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D66" s="11" t="n">
-        <v>62.5</v>
+      <c r="D66" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F66" s="11" t="n">
-        <v>437.5</v>
+        <v>5</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>325</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>73.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -3291,23 +3291,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D67" s="9" t="n">
-        <v>62.5</v>
+      <c r="D67" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>325</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3320,17 +3320,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D68" s="11" t="n">
-        <v>62.5</v>
+      <c r="D68" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F68" s="11" t="n">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3349,17 +3349,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n">
-        <v>62.5</v>
+      <c r="D69" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>67.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70">
@@ -3378,144 +3378,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D70" s="11" t="n">
-        <v>72.2</v>
+      <c r="D70" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>72.2</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>12.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="n">
-        <v>20</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>22.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>437.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>45</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" s="10" t="n">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3523,28 +3523,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
-        <v>20</v>
+      <c r="D75" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -3552,28 +3552,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
-        <v>40</v>
+      <c r="D76" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F76" s="10" t="n">
-        <v>320</v>
+        <v>3</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>48</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -3581,133 +3581,133 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
-        <v>50</v>
+      <c r="D77" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>250</v>
+        <v>1</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>56.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>72</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>72</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="82">
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>75.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>71.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>25</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -3814,22 +3814,22 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>56.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -3875,24 +3875,24 @@
         <v>60</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -3901,27 +3901,27 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3930,27 +3930,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>56.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -3958,28 +3958,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D90" s="11" t="n">
-        <v>57.5</v>
+      <c r="D90" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F90" s="11" t="n">
-        <v>345</v>
+        <v>1</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>66.09999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3987,28 +3987,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D91" s="9" t="n">
-        <v>57.5</v>
+      <c r="D91" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F91" s="9" t="n">
-        <v>460</v>
+        <v>10</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -4016,28 +4016,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D92" s="11" t="n">
-        <v>57.5</v>
+      <c r="D92" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>345</v>
+        <v>8</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>66.09999999999999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -4045,28 +4045,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D93" s="9" t="n">
-        <v>67.5</v>
+      <c r="D93" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" s="9" t="n">
-        <v>135</v>
+        <v>5</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -4075,22 +4075,22 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -4104,22 +4104,22 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -4136,19 +4136,19 @@
         <v>50</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -4161,23 +4161,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
-        <v>55</v>
+      <c r="D97" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F97" s="8" t="n">
-        <v>440</v>
+        <v>6</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -4190,23 +4190,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n">
-        <v>55</v>
+      <c r="D98" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F98" s="10" t="n">
-        <v>440</v>
+      <c r="F98" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -4219,23 +4219,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
-        <v>55</v>
+      <c r="D99" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <v>275</v>
+        <v>6</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>61.9</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -4248,220 +4248,220 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n">
-        <v>65</v>
+      <c r="D100" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>65</v>
+        <v>2</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>66.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E101" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="F101" s="8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>11.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F102" s="10" t="n">
         <v>240</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>45</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>62.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -4481,16 +4481,16 @@
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>69</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="109">
@@ -4510,16 +4510,16 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>67.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110">
@@ -4542,19 +4542,19 @@
         <v>40</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -4564,26 +4564,26 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -4593,26 +4593,26 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -4622,26 +4622,26 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
         <v>50</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -4651,26 +4651,26 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F114" s="11" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>500</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>60.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -4680,26 +4680,26 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F115" s="9" t="n">
-        <v>315</v>
+      <c r="F115" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>60.4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -4709,26 +4709,26 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D116" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" s="11" t="n">
-        <v>420</v>
+        <v>5</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>63</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -4738,20 +4738,20 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E117" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F117" s="9" t="n">
-        <v>420</v>
+      <c r="F117" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118">
@@ -4770,17 +4770,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D118" s="11" t="n">
-        <v>52.5</v>
+      <c r="D118" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F118" s="11" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>60.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -4799,28 +4799,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D119" s="9" t="n">
-        <v>62.5</v>
+      <c r="D119" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>125</v>
+        <v>6</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>65.59999999999999</v>
+        <v>46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -4829,27 +4829,27 @@
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>25</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4857,28 +4857,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D121" s="8" t="n">
-        <v>40</v>
+      <c r="D121" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <v>320</v>
+        <v>6</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>48</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -4886,28 +4886,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n">
-        <v>50</v>
+      <c r="D122" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4915,28 +4915,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D123" s="8" t="n">
-        <v>50</v>
+      <c r="D123" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E123" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F123" s="8" t="n">
-        <v>400</v>
+      <c r="F123" s="9" t="n">
+        <v>420</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -4944,28 +4944,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n">
-        <v>50</v>
+      <c r="D124" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F124" s="10" t="n">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>420</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>57.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4973,310 +4973,513 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n">
-        <v>50</v>
+      <c r="D125" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F125" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="G126" s="11" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="n">
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G128" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G129" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E126" s="10" t="n">
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G130" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E133" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F126" s="10" t="n">
+      <c r="F133" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="G126" s="11" t="n">
+      <c r="G133" s="9" t="n">
         <v>64.5</v>
       </c>
     </row>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="13" t="inlineStr">
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
         <is>
           <t>週別集計</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>最大重量 (kg)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>推定1RM (kg)</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>総Volume (kg)</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>セッション数</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>セット数</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B130" s="8" t="n">
+      <c r="B137" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C130" s="9" t="n">
+      <c r="C137" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="D130" s="9" t="n">
+      <c r="D137" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="E130" s="8" t="n">
+      <c r="E137" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="8" t="n">
+      <c r="F137" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>2026-W13</t>
         </is>
       </c>
-      <c r="B131" s="11" t="n">
+      <c r="B138" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="C131" s="11" t="n">
+      <c r="C138" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D138" s="11" t="n">
         <v>5670</v>
       </c>
-      <c r="E131" s="10" t="n">
+      <c r="E138" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F131" s="10" t="n">
+      <c r="F138" s="10" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>2026-W14</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
+      <c r="B139" s="9" t="n">
         <v>67.5</v>
       </c>
-      <c r="C132" s="9" t="n">
+      <c r="C139" s="9" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="D132" s="9" t="n">
+      <c r="D139" s="9" t="n">
         <v>3545</v>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E139" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F139" s="8" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>2026-W15</t>
         </is>
       </c>
-      <c r="B133" s="10" t="n">
+      <c r="B140" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="C133" s="11" t="n">
+      <c r="C140" s="11" t="n">
         <v>75.2</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D140" s="11" t="n">
         <v>3980</v>
       </c>
-      <c r="E133" s="10" t="n">
+      <c r="E140" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F133" s="10" t="n">
+      <c r="F140" s="10" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>2026-W16</t>
         </is>
       </c>
-      <c r="B134" s="8" t="n">
+      <c r="B141" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="C134" s="9" t="n">
+      <c r="C141" s="9" t="n">
         <v>53.8</v>
       </c>
-      <c r="D134" s="9" t="n">
+      <c r="D141" s="9" t="n">
         <v>550</v>
       </c>
-      <c r="E134" s="8" t="n">
+      <c r="E141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F141" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>2026-W17</t>
         </is>
       </c>
-      <c r="B135" s="10" t="n">
+      <c r="B142" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="C135" s="11" t="n">
+      <c r="C142" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D142" s="11" t="n">
         <v>5967.2</v>
       </c>
-      <c r="E135" s="10" t="n">
+      <c r="E142" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F135" s="10" t="n">
+      <c r="F142" s="10" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
+      <c r="B143" s="9" t="n">
         <v>77.5</v>
       </c>
-      <c r="C136" s="9" t="n">
+      <c r="C143" s="9" t="n">
         <v>80.5</v>
       </c>
-      <c r="D136" s="9" t="n">
+      <c r="D143" s="9" t="n">
         <v>5355</v>
       </c>
-      <c r="E136" s="8" t="n">
+      <c r="E143" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F136" s="8" t="n">
+      <c r="F143" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>2026-W19</t>
         </is>
       </c>
-      <c r="B137" s="10" t="n">
+      <c r="B144" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="C137" s="11" t="n">
+      <c r="C144" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D144" s="11" t="n">
         <v>6122.5</v>
       </c>
-      <c r="E137" s="10" t="n">
+      <c r="E144" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F137" s="10" t="n">
+      <c r="F144" s="10" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>2026-W20</t>
         </is>
       </c>
-      <c r="B138" s="8" t="n">
+      <c r="B145" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="C138" s="9" t="n">
+      <c r="C145" s="9" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="D138" s="9" t="n">
+      <c r="D145" s="9" t="n">
         <v>2045</v>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E145" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F138" s="8" t="n">
+      <c r="F145" s="8" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>2026-W21</t>
         </is>
       </c>
-      <c r="B139" s="11" t="n">
+      <c r="B146" s="11" t="n">
         <v>77.5</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="D139" s="11" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="10" t="n">
-        <v>6</v>
+      <c r="C146" s="11" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A135:G135"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$137:$A$146</f>
+              <f>'ベンチプレス'!$A$144:$A$154</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$137:$C$146</f>
+              <f>'ベンチプレス'!$C$144:$C$154</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>141</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-05-25）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-06-01）</t>
         </is>
       </c>
     </row>
@@ -1151,228 +1151,248 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
-      <c r="F11" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1260</v>
+      </c>
       <c r="H12" s="9" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="11" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="11" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>2540</v>
+      </c>
       <c r="H16" s="9" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
-      <c r="F17" s="11" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
       <c r="H17" s="11" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="9" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>3290</v>
+      </c>
       <c r="H18" s="9" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="11" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B20" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C20" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D20" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>1120</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>57.5</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>1350</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H20" s="9" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1391,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1451,12 +1471,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1480,12 +1500,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1509,12 +1529,12 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1523,27 +1543,27 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1551,28 +1571,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>77.5</v>
+      <c r="D7" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>542.5</v>
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>140</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1580,28 +1600,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>77.5</v>
+      <c r="D8" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>465</v>
+        <v>3</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>240</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1609,28 +1629,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>77.5</v>
+      <c r="D9" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>465</v>
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1638,23 +1658,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>77.5</v>
+      <c r="D10" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>232.5</v>
+        <v>6</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>360</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>83.3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1683,7 +1703,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1712,7 +1732,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1741,7 +1761,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1758,19 +1778,19 @@
         <v>77.5</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>310</v>
+        <v>542.5</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>85.2</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1787,19 +1807,19 @@
         <v>77.5</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>81.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1812,231 +1832,231 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>60</v>
+      <c r="D16" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>465</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>67.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>20</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>232.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>25</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>57.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>525</v>
+        <v>195</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>450</v>
+        <v>4</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>310</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>86.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>375</v>
+        <v>2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>155</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>84.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>25</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2045,27 +2065,27 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2074,27 +2094,27 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>300</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>67.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2103,27 +2123,27 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>71.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2131,28 +2151,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>72.5</v>
+      <c r="D27" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>507.5</v>
+      <c r="F27" s="8" t="n">
+        <v>525</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>85.2</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2160,28 +2180,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>72.5</v>
+      <c r="D28" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>580</v>
+        <v>6</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>450</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>87</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2189,17 +2209,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>72.5</v>
+      <c r="D29" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>435</v>
+        <v>5</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>375</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2218,23 +2238,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
-        <v>62.5</v>
+      <c r="D30" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>750</v>
+        <v>10</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>81.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2248,22 +2268,22 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -2277,22 +2297,22 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>60</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2306,22 +2326,22 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>64.5</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2334,23 +2354,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>70</v>
+      <c r="D34" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>560</v>
+        <v>7</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>507.5</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>84</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2363,23 +2383,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
-        <v>70</v>
+      <c r="D35" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F35" s="8" t="n">
-        <v>560</v>
+      <c r="F35" s="9" t="n">
+        <v>580</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2392,23 +2412,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>70</v>
+      <c r="D36" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>420</v>
+      <c r="F36" s="11" t="n">
+        <v>435</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>80.5</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2421,17 +2441,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
-        <v>80</v>
+      <c r="D37" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>80</v>
+        <v>12</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>750</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>82</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="38">
@@ -2451,27 +2471,27 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2480,27 +2500,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2509,27 +2529,27 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>50</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -2538,27 +2558,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>58.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2567,27 +2587,27 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>61.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2596,27 +2616,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>65</v>
+        <v>420</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2625,27 +2645,27 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>78.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -2654,16 +2674,16 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>80.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
@@ -2683,16 +2703,16 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>75.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -2712,16 +2732,16 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -2744,19 +2764,19 @@
         <v>50</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>57.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -2770,22 +2790,22 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>25</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -2799,22 +2819,22 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>48</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -2828,22 +2848,22 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>57.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -2857,22 +2877,22 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>61.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -2885,23 +2905,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D53" s="9" t="n">
-        <v>67.5</v>
+      <c r="D53" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>337.5</v>
+        <v>3</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>210</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2914,23 +2934,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n">
-        <v>67.5</v>
+      <c r="D54" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F54" s="11" t="n">
-        <v>472.5</v>
+        <v>4</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>280</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>79.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -2943,17 +2963,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D55" s="9" t="n">
-        <v>67.5</v>
+      <c r="D55" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>270</v>
+        <v>6</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>74.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="56">
@@ -2972,17 +2992,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D56" s="11" t="n">
-        <v>67.5</v>
+      <c r="D56" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="11" t="n">
-        <v>202.5</v>
+        <v>10</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>72.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -3001,17 +3021,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>77.5</v>
+      <c r="D57" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="9" t="n">
-        <v>77.5</v>
+        <v>8</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -3031,27 +3051,27 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>72</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -3060,27 +3080,27 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>25</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3088,28 +3108,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
-        <v>40</v>
+      <c r="D60" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>400</v>
+        <v>5</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>337.5</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>50</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -3117,28 +3137,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
-        <v>50</v>
+      <c r="D61" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>250</v>
+        <v>7</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>472.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>56.2</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3146,28 +3166,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n">
-        <v>65</v>
+      <c r="D62" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>195</v>
+        <v>4</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>270</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -3175,28 +3195,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n">
-        <v>65</v>
+      <c r="D63" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F63" s="8" t="n">
-        <v>520</v>
+        <v>3</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>202.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>78</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3204,28 +3224,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n">
-        <v>65</v>
+      <c r="D64" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>455</v>
+        <v>1</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -3234,16 +3254,16 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>195</v>
+        <v>480</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66">
@@ -3263,16 +3283,16 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
@@ -3292,16 +3312,16 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -3321,22 +3341,22 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>76.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3350,22 +3370,22 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>35</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -3379,22 +3399,22 @@
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -3408,22 +3428,22 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>53.8</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -3436,23 +3456,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D72" s="11" t="n">
-        <v>62.5</v>
+      <c r="D72" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>500</v>
+        <v>3</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>75</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -3465,23 +3485,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D73" s="9" t="n">
-        <v>62.5</v>
+      <c r="D73" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>437.5</v>
+        <v>5</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>325</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>73.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -3494,23 +3514,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D74" s="11" t="n">
-        <v>62.5</v>
+      <c r="D74" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F74" s="11" t="n">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>325</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -3523,17 +3543,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="9" t="n">
-        <v>62.5</v>
+      <c r="D75" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3552,17 +3572,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="11" t="n">
-        <v>62.5</v>
+      <c r="D76" s="10" t="n">
+        <v>28</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" s="11" t="n">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>280</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>67.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77">
@@ -3581,144 +3601,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>72.2</v>
+      <c r="D77" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="9" t="n">
-        <v>72.2</v>
+        <v>10</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>12.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>20</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>22.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F80" s="10" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>437.5</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>45</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -3726,28 +3746,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n">
-        <v>20</v>
+      <c r="D82" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F82" s="10" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -3755,28 +3775,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
-        <v>40</v>
+      <c r="D83" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>320</v>
+        <v>3</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>187.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>48</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -3784,133 +3804,133 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n">
-        <v>50</v>
+      <c r="D84" s="11" t="n">
+        <v>72.2</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>250</v>
+        <v>1</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>72.2</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>56.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>72</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>72</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="89">
@@ -3930,16 +3950,16 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>75.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -3959,22 +3979,22 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>71.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -3988,22 +4008,22 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>25</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -4017,22 +4037,22 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -4046,22 +4066,22 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>56.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -4078,24 +4098,24 @@
         <v>60</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -4104,27 +4124,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -4133,27 +4153,27 @@
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>56.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -4161,28 +4181,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n">
-        <v>57.5</v>
+      <c r="D97" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>345</v>
+        <v>1</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -4190,28 +4210,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="11" t="n">
-        <v>57.5</v>
+      <c r="D98" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F98" s="11" t="n">
-        <v>460</v>
+        <v>10</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -4219,28 +4239,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
-        <v>57.5</v>
+      <c r="D99" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" s="9" t="n">
-        <v>345</v>
+        <v>8</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -4248,28 +4268,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D100" s="11" t="n">
-        <v>67.5</v>
+      <c r="D100" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F100" s="11" t="n">
-        <v>135</v>
+        <v>5</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>250</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -4278,22 +4298,22 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -4307,22 +4327,22 @@
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -4339,19 +4359,19 @@
         <v>50</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -4364,23 +4384,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n">
-        <v>55</v>
+      <c r="D104" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>440</v>
+        <v>6</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>345</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -4393,23 +4413,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
-        <v>55</v>
+      <c r="D105" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F105" s="8" t="n">
-        <v>440</v>
+      <c r="F105" s="9" t="n">
+        <v>460</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -4422,23 +4442,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n">
-        <v>55</v>
+      <c r="D106" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F106" s="10" t="n">
-        <v>275</v>
+        <v>6</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>345</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>61.9</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -4451,220 +4471,220 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D107" s="8" t="n">
-        <v>65</v>
+      <c r="D107" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="8" t="n">
-        <v>65</v>
+        <v>2</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>135</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E108" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="E108" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="F108" s="10" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>11.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F109" s="8" t="n">
         <v>240</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>45</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E112" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>62.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -4684,16 +4704,16 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>69</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="116">
@@ -4713,16 +4733,16 @@
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>67.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117">
@@ -4745,19 +4765,19 @@
         <v>40</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -4767,26 +4787,26 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
@@ -4796,26 +4816,26 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -4825,26 +4845,26 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -4854,26 +4874,26 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>500</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>60.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -4883,26 +4903,26 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D122" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E122" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F122" s="11" t="n">
-        <v>315</v>
+      <c r="F122" s="10" t="n">
+        <v>360</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>60.4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
@@ -4912,26 +4932,26 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F123" s="9" t="n">
-        <v>420</v>
+        <v>5</v>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>63</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -4941,20 +4961,20 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D124" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E124" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F124" s="11" t="n">
-        <v>420</v>
+      <c r="F124" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125">
@@ -4973,17 +4993,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D125" s="9" t="n">
-        <v>52.5</v>
+      <c r="D125" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F125" s="9" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>60.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126">
@@ -5002,28 +5022,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D126" s="11" t="n">
-        <v>62.5</v>
+      <c r="D126" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F126" s="11" t="n">
-        <v>125</v>
+        <v>6</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>240</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>65.59999999999999</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -5032,27 +5052,27 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>25</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
@@ -5060,28 +5080,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n">
-        <v>40</v>
+      <c r="D128" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>320</v>
+        <v>6</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>48</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -5089,28 +5109,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D129" s="8" t="n">
-        <v>50</v>
+      <c r="D129" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F129" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -5118,28 +5138,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n">
-        <v>50</v>
+      <c r="D130" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E130" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F130" s="10" t="n">
-        <v>400</v>
+      <c r="F130" s="11" t="n">
+        <v>420</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
@@ -5147,28 +5167,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D131" s="8" t="n">
-        <v>50</v>
+      <c r="D131" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F131" s="8" t="n">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>420</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>57.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -5176,310 +5196,535 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D132" s="10" t="n">
-        <v>50</v>
+      <c r="D132" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F132" s="10" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="G133" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="n">
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G134" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F135" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G136" s="11" t="n">
         <v>60</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F133" s="8" t="n">
-        <v>180</v>
-      </c>
-      <c r="G133" s="9" t="n">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="13" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="n">
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G137" s="9" t="n">
         <v>60</v>
-      </c>
-      <c r="C137" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="D137" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B138" s="11" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="C138" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="D138" s="11" t="n">
-        <v>5670</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>19</v>
+        <v>300</v>
+      </c>
+      <c r="G138" s="11" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C139" s="9" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D139" s="9" t="n">
-        <v>3545</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>13</v>
+        <v>400</v>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G140" s="11" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="D145" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>3545</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
           <t>2026-W15</t>
         </is>
       </c>
-      <c r="B140" s="10" t="n">
+      <c r="B147" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="C140" s="11" t="n">
+      <c r="C147" s="11" t="n">
         <v>75.2</v>
       </c>
-      <c r="D140" s="11" t="n">
+      <c r="D147" s="11" t="n">
         <v>3980</v>
       </c>
-      <c r="E140" s="10" t="n">
+      <c r="E147" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F140" s="10" t="n">
+      <c r="F147" s="10" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>2026-W16</t>
         </is>
       </c>
-      <c r="B141" s="8" t="n">
+      <c r="B148" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="C141" s="9" t="n">
+      <c r="C148" s="9" t="n">
         <v>53.8</v>
       </c>
-      <c r="D141" s="9" t="n">
+      <c r="D148" s="9" t="n">
         <v>550</v>
       </c>
-      <c r="E141" s="8" t="n">
+      <c r="E148" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="F148" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="10" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>2026-W17</t>
         </is>
       </c>
-      <c r="B142" s="10" t="n">
+      <c r="B149" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="C142" s="11" t="n">
+      <c r="C149" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="D142" s="11" t="n">
+      <c r="D149" s="11" t="n">
         <v>5967.2</v>
       </c>
-      <c r="E142" s="10" t="n">
+      <c r="E149" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F142" s="10" t="n">
+      <c r="F149" s="10" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
+      <c r="B150" s="9" t="n">
         <v>77.5</v>
       </c>
-      <c r="C143" s="9" t="n">
+      <c r="C150" s="9" t="n">
         <v>80.5</v>
       </c>
-      <c r="D143" s="9" t="n">
+      <c r="D150" s="9" t="n">
         <v>5355</v>
       </c>
-      <c r="E143" s="8" t="n">
+      <c r="E150" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F143" s="8" t="n">
+      <c r="F150" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>2026-W19</t>
         </is>
       </c>
-      <c r="B144" s="10" t="n">
+      <c r="B151" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="C144" s="11" t="n">
+      <c r="C151" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="D144" s="11" t="n">
+      <c r="D151" s="11" t="n">
         <v>6122.5</v>
       </c>
-      <c r="E144" s="10" t="n">
+      <c r="E151" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F144" s="10" t="n">
+      <c r="F151" s="10" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>2026-W20</t>
         </is>
       </c>
-      <c r="B145" s="8" t="n">
+      <c r="B152" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="C145" s="9" t="n">
+      <c r="C152" s="9" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="D145" s="9" t="n">
+      <c r="D152" s="9" t="n">
         <v>2045</v>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E152" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F152" s="8" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
         <is>
           <t>2026-W21</t>
         </is>
       </c>
-      <c r="B146" s="11" t="n">
+      <c r="B153" s="11" t="n">
         <v>77.5</v>
       </c>
-      <c r="C146" s="11" t="n">
+      <c r="C153" s="11" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="D146" s="11" t="n">
+      <c r="D153" s="11" t="n">
         <v>4060</v>
       </c>
-      <c r="E146" s="10" t="n">
+      <c r="E153" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F146" s="10" t="n">
+      <c r="F153" s="10" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A142:G142"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$144:$A$154</f>
+              <f>'ベンチプレス'!$A$159:$A$170</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$144:$C$154</f>
+              <f>'ベンチプレス'!$C$159:$C$170</f>
             </numRef>
           </val>
         </ser>
@@ -438,12 +438,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'デッドリフト'!$A$17</f>
+              <f>'デッドリフト'!$A$17:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'デッドリフト'!$C$17</f>
+              <f>'デッドリフト'!$C$17:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>141</row>
+      <row>156</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-06-01）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-06-08）</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1052,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1070,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1151,248 +1151,272 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W23</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>86</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+        <v>5140</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2700</v>
+      </c>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>1600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="F13" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>1260</v>
+      </c>
       <c r="H13" s="11" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="9" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="9" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="11" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="F17" s="11" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>2540</v>
+      </c>
       <c r="H17" s="11" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
+      <c r="F19" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>3290</v>
+      </c>
       <c r="H19" s="11" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="9" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B21" s="11" t="n">
         <v>64.5</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C21" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E21" s="11" t="n">
         <v>1120</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F21" s="11" t="n">
         <v>57.5</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G21" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H21" s="11" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1411,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1471,12 +1495,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1500,12 +1524,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1529,12 +1553,12 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1543,27 +1567,27 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>64.5</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1587,12 +1611,12 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1600,28 +1624,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>80</v>
+      <c r="D8" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>240</v>
+        <v>6</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>495</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>86</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1629,28 +1653,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>80</v>
+      <c r="D9" s="9" t="n">
+        <v>82.5</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>80</v>
+        <v>5</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>412.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>82</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1658,28 +1682,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>60</v>
+      <c r="D10" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>360</v>
+        <v>7</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>577.5</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>69</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1688,27 +1712,27 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1717,27 +1741,27 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1746,27 +1770,27 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1774,28 +1798,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>77.5</v>
+      <c r="D14" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>542.5</v>
+        <v>3</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1803,28 +1827,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>77.5</v>
+      <c r="D15" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>465</v>
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>150</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1832,28 +1856,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>77.5</v>
+      <c r="D16" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>465</v>
+      <c r="F16" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1861,28 +1885,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>77.5</v>
+      <c r="D17" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>232.5</v>
+        <v>6</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>480</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>83.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1891,27 +1915,27 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1920,27 +1944,27 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1949,27 +1973,27 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1977,28 +2001,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>77.5</v>
+      <c r="D21" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>310</v>
+        <v>3</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>180</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>85.2</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2006,28 +2030,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>77.5</v>
+      <c r="D22" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>155</v>
+      <c r="F22" s="10" t="n">
+        <v>140</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>81.40000000000001</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2036,462 +2060,462 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>67.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>57.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>525</v>
+        <v>400</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>450</v>
+        <v>195</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>86.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>375</v>
+        <v>7</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>542.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>84.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>20</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>465</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>25</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>50</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>465</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>60</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>60</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>232.5</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>67.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>71.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>72.5</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>507.5</v>
+        <v>8</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>85.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>72.5</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>580</v>
+        <v>3</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>195</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>87</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>435</v>
+        <v>310</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>83.40000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>750</v>
+        <v>155</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>25</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2500,27 +2524,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2529,27 +2553,27 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>64.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -2558,27 +2582,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>560</v>
+        <v>195</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>84</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2587,27 +2611,27 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>84</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2616,27 +2640,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>80.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2645,22 +2669,22 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>82</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -2674,27 +2698,27 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2703,27 +2727,27 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2732,27 +2756,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>50</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2761,27 +2785,27 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>58.8</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2789,28 +2813,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
-        <v>60</v>
+      <c r="D49" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="8" t="n">
-        <v>60</v>
+        <v>7</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>61.5</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2818,28 +2842,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n">
-        <v>65</v>
+      <c r="D50" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="10" t="n">
-        <v>65</v>
+        <v>8</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>66.59999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2847,28 +2871,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
-        <v>70</v>
+      <c r="D51" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F51" s="8" t="n">
-        <v>350</v>
+        <v>6</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>78.8</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -2876,28 +2900,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n">
-        <v>70</v>
+      <c r="D52" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <v>420</v>
+        <v>12</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>80.5</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2906,27 +2930,27 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>75.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -2935,27 +2959,27 @@
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2964,27 +2988,27 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>57.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -2993,27 +3017,27 @@
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -3022,27 +3046,27 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>320</v>
+        <v>560</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3051,27 +3075,27 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>6</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>57.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -3080,27 +3104,27 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>61.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3108,23 +3132,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D60" s="11" t="n">
-        <v>67.5</v>
+      <c r="D60" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>337.5</v>
+        <v>8</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>75.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3137,23 +3161,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D61" s="9" t="n">
-        <v>67.5</v>
+      <c r="D61" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>472.5</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>79.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3166,23 +3190,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D62" s="11" t="n">
-        <v>67.5</v>
+      <c r="D62" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F62" s="11" t="n">
-        <v>270</v>
+        <v>10</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>74.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3195,23 +3219,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D63" s="9" t="n">
-        <v>67.5</v>
+      <c r="D63" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>202.5</v>
+        <v>7</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>350</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>72.59999999999999</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3224,23 +3248,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D64" s="11" t="n">
-        <v>77.5</v>
+      <c r="D64" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="11" t="n">
-        <v>77.5</v>
+      <c r="F64" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>79.40000000000001</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3254,27 +3278,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>480</v>
+        <v>65</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>72</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3283,27 +3307,27 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>25</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -3312,27 +3336,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>50</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3341,27 +3365,27 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>56.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3370,27 +3394,27 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>195</v>
+        <v>280</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3399,27 +3423,27 @@
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>78</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -3428,27 +3452,27 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>455</v>
+        <v>200</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>76.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -3457,27 +3481,27 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>195</v>
+        <v>320</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -3486,27 +3510,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -3515,27 +3539,27 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>325</v>
+        <v>60</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3543,28 +3567,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
-        <v>75</v>
+      <c r="D75" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>75</v>
+        <v>5</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>337.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -3572,28 +3596,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
-        <v>28</v>
+      <c r="D76" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F76" s="10" t="n">
-        <v>280</v>
+        <v>7</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>35</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -3601,28 +3625,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
-        <v>40</v>
+      <c r="D77" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>400</v>
+        <v>4</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>50</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -3630,28 +3654,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n">
-        <v>50</v>
+      <c r="D78" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F78" s="10" t="n">
-        <v>150</v>
+      <c r="F78" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>53.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -3660,27 +3684,27 @@
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>500</v>
+        <v>77.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>75</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -3688,23 +3712,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D80" s="11" t="n">
-        <v>62.5</v>
+      <c r="D80" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F80" s="11" t="n">
-        <v>437.5</v>
+        <v>8</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -3717,23 +3741,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D81" s="9" t="n">
-        <v>62.5</v>
+      <c r="D81" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F81" s="9" t="n">
-        <v>500</v>
+        <v>10</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -3746,23 +3770,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D82" s="11" t="n">
-        <v>62.5</v>
+      <c r="D82" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F82" s="11" t="n">
-        <v>500</v>
+        <v>10</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -3775,23 +3799,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
-        <v>62.5</v>
+      <c r="D83" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>187.5</v>
+        <v>5</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>67.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -3804,144 +3828,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D84" s="11" t="n">
-        <v>72.2</v>
+      <c r="D84" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="11" t="n">
-        <v>72.2</v>
+        <v>3</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>74</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>100</v>
+        <v>520</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>12.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>100</v>
+        <v>455</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>22.5</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>45</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>53.8</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3950,27 +3974,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>25</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -3979,27 +4003,27 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>48</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -4008,27 +4032,27 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>56.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -4037,27 +4061,27 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -4066,27 +4090,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -4094,28 +4118,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n">
-        <v>60</v>
+      <c r="D94" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F94" s="10" t="n">
-        <v>480</v>
+      <c r="F94" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -4123,28 +4147,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D95" s="8" t="n">
-        <v>60</v>
+      <c r="D95" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F95" s="8" t="n">
-        <v>480</v>
+        <v>7</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>437.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -4152,28 +4176,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n">
-        <v>70</v>
+      <c r="D96" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>210</v>
+        <v>8</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>75.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -4181,28 +4205,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
-        <v>70</v>
+      <c r="D97" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="8" t="n">
-        <v>70</v>
+        <v>8</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>71.8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -4210,28 +4234,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n">
-        <v>20</v>
+      <c r="D98" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" s="10" t="n">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>25</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -4239,144 +4263,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
-        <v>40</v>
+      <c r="D99" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <v>320</v>
+        <v>1</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>56.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>66</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F102" s="10" t="n">
         <v>200</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
         <v>50</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
@@ -4384,28 +4408,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="11" t="n">
-        <v>57.5</v>
+      <c r="D104" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F104" s="11" t="n">
-        <v>345</v>
+        <v>10</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>66.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -4413,28 +4437,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D105" s="9" t="n">
-        <v>57.5</v>
+      <c r="D105" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F105" s="9" t="n">
-        <v>460</v>
+      <c r="F105" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
@@ -4442,28 +4466,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D106" s="11" t="n">
-        <v>57.5</v>
+      <c r="D106" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F106" s="11" t="n">
-        <v>345</v>
+        <v>5</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>250</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>66.09999999999999</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -4471,28 +4495,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D107" s="9" t="n">
-        <v>67.5</v>
+      <c r="D107" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>135</v>
+        <v>8</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>480</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
@@ -4501,27 +4525,27 @@
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -4530,27 +4554,27 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -4559,27 +4583,27 @@
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>53.8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -4588,27 +4612,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>440</v>
+        <v>210</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>66</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -4617,27 +4641,27 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>66</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -4646,27 +4670,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>61.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -4675,317 +4699,317 @@
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>66.59999999999999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>11.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="10" t="n">
         <v>240</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F117" s="8" t="n">
         <v>200</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F119" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>60</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F120" s="10" t="n">
-        <v>400</v>
+      <c r="F120" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <v>500</v>
+        <v>6</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>62.5</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="n">
-        <v>60</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>360</v>
+        <v>2</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>67.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
         <v>40</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4994,27 +5018,27 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>25</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
@@ -5023,27 +5047,27 @@
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -5052,27 +5076,27 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>53.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
@@ -5080,28 +5104,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D128" s="11" t="n">
-        <v>52.5</v>
+      <c r="D128" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F128" s="11" t="n">
-        <v>315</v>
+        <v>5</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>275</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>60.4</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -5109,23 +5133,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D129" s="9" t="n">
-        <v>52.5</v>
+      <c r="D129" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>315</v>
+        <v>1</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>60.4</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -5135,26 +5159,26 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D130" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F130" s="11" t="n">
-        <v>420</v>
+        <v>5</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>63</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -5164,26 +5188,26 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F131" s="9" t="n">
-        <v>420</v>
+      <c r="F131" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -5193,26 +5217,26 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>315</v>
+        <v>5</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>60.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -5222,509 +5246,966 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="n">
-        <v>62.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>125</v>
+        <v>8</v>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>65.59999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>300</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>57.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G140" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="G141" s="9" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G142" s="11" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="G143" s="9" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="G144" s="11" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>420</v>
+      </c>
+      <c r="G145" s="9" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="G146" s="11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="G147" s="9" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="G148" s="11" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C140" s="10" t="inlineStr">
-        <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="n">
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F149" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G149" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G150" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F151" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G151" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E140" s="10" t="n">
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G152" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G153" s="9" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G154" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E155" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F140" s="10" t="n">
+      <c r="F155" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="G140" s="11" t="n">
+      <c r="G155" s="9" t="n">
         <v>64.5</v>
       </c>
     </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="13" t="inlineStr">
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="13" t="inlineStr">
         <is>
           <t>週別集計</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>最大重量 (kg)</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>推定1RM (kg)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>総Volume (kg)</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>セッション数</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>セット数</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B144" s="8" t="n">
+      <c r="B159" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C144" s="9" t="n">
+      <c r="C159" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="D144" s="9" t="n">
+      <c r="D159" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="E144" s="8" t="n">
+      <c r="E159" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F159" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="10" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
         <is>
           <t>2026-W13</t>
         </is>
       </c>
-      <c r="B145" s="11" t="n">
+      <c r="B160" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="C145" s="11" t="n">
+      <c r="C160" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="D145" s="11" t="n">
+      <c r="D160" s="11" t="n">
         <v>5670</v>
       </c>
-      <c r="E145" s="10" t="n">
+      <c r="E160" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F145" s="10" t="n">
+      <c r="F160" s="10" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>2026-W14</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
+      <c r="B161" s="9" t="n">
         <v>67.5</v>
       </c>
-      <c r="C146" s="9" t="n">
+      <c r="C161" s="9" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="D146" s="9" t="n">
+      <c r="D161" s="9" t="n">
         <v>3545</v>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E161" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F161" s="8" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
         <is>
           <t>2026-W15</t>
         </is>
       </c>
-      <c r="B147" s="10" t="n">
+      <c r="B162" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C162" s="11" t="n">
         <v>75.2</v>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D162" s="11" t="n">
         <v>3980</v>
       </c>
-      <c r="E147" s="10" t="n">
+      <c r="E162" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F147" s="10" t="n">
+      <c r="F162" s="10" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>2026-W16</t>
         </is>
       </c>
-      <c r="B148" s="8" t="n">
+      <c r="B163" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="C148" s="9" t="n">
+      <c r="C163" s="9" t="n">
         <v>53.8</v>
       </c>
-      <c r="D148" s="9" t="n">
+      <c r="D163" s="9" t="n">
         <v>550</v>
       </c>
-      <c r="E148" s="8" t="n">
+      <c r="E163" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F148" s="8" t="n">
+      <c r="F163" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="10" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
         <is>
           <t>2026-W17</t>
         </is>
       </c>
-      <c r="B149" s="10" t="n">
+      <c r="B164" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="C149" s="11" t="n">
+      <c r="C164" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="D149" s="11" t="n">
+      <c r="D164" s="11" t="n">
         <v>5967.2</v>
       </c>
-      <c r="E149" s="10" t="n">
+      <c r="E164" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F149" s="10" t="n">
+      <c r="F164" s="10" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="8" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="B150" s="9" t="n">
+      <c r="B165" s="9" t="n">
         <v>77.5</v>
       </c>
-      <c r="C150" s="9" t="n">
+      <c r="C165" s="9" t="n">
         <v>80.5</v>
       </c>
-      <c r="D150" s="9" t="n">
+      <c r="D165" s="9" t="n">
         <v>5355</v>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E165" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F165" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="10" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
         <is>
           <t>2026-W19</t>
         </is>
       </c>
-      <c r="B151" s="10" t="n">
+      <c r="B166" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="C151" s="11" t="n">
+      <c r="C166" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="D151" s="11" t="n">
+      <c r="D166" s="11" t="n">
         <v>6122.5</v>
       </c>
-      <c r="E151" s="10" t="n">
+      <c r="E166" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F151" s="10" t="n">
+      <c r="F166" s="10" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="8" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t>2026-W20</t>
         </is>
       </c>
-      <c r="B152" s="8" t="n">
+      <c r="B167" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="C152" s="9" t="n">
+      <c r="C167" s="9" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="D152" s="9" t="n">
+      <c r="D167" s="9" t="n">
         <v>2045</v>
       </c>
-      <c r="E152" s="8" t="n">
+      <c r="E167" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F152" s="8" t="n">
+      <c r="F167" s="8" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="10" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
         <is>
           <t>2026-W21</t>
         </is>
       </c>
-      <c r="B153" s="11" t="n">
+      <c r="B168" s="11" t="n">
         <v>77.5</v>
       </c>
-      <c r="C153" s="11" t="n">
+      <c r="C168" s="11" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="D153" s="11" t="n">
+      <c r="D168" s="11" t="n">
         <v>4060</v>
       </c>
-      <c r="E153" s="10" t="n">
+      <c r="E168" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="10" t="n">
+      <c r="F168" s="10" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>2026-W22</t>
         </is>
       </c>
-      <c r="B154" s="8" t="n">
+      <c r="B169" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="C154" s="9" t="n">
+      <c r="C169" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="D154" s="9" t="n">
+      <c r="D169" s="9" t="n">
         <v>1600</v>
       </c>
-      <c r="E154" s="8" t="n">
+      <c r="E169" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F154" s="8" t="n">
+      <c r="F169" s="8" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C170" s="11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A142:G142"/>
+    <mergeCell ref="A157:G157"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5738,7 +6219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5798,116 +6279,261 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Deadlift (Barbell)</t>
+          <t>デッドリフト　（バーベル）</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>87.2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Deadlift (Barbell)</t>
+          <t>デッドリフト　（バーベル）</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
         <v>80</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>87.2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Deadlift (Barbell)</t>
+          <t>デッドリフト　（バーベル）</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>87.2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Deadlift (Barbell)</t>
+          <t>デッドリフト　（バーベル）</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F7" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>デッドリフト　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Deadlift (Barbell)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G12" s="11" t="n">
         <v>92</v>
       </c>
     </row>
@@ -5970,6 +6596,28 @@
       </c>
       <c r="F17" s="8" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$159:$A$170</f>
+              <f>'ベンチプレス'!$A$167:$A$179</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$159:$C$170</f>
+              <f>'ベンチプレス'!$C$167:$C$179</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>164</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-06-08）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-06-15）</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -1151,272 +1151,292 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W23</t>
+          <t>2026-W24</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>96.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>5140</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>2700</v>
-      </c>
+        <v>1465</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>7840</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W23</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>86</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
+        <v>5140</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>2700</v>
+      </c>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>1600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1260</v>
+      </c>
       <c r="H14" s="9" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="11" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>2540</v>
+      </c>
       <c r="H18" s="9" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
-      <c r="F19" s="11" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
       <c r="H19" s="11" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="9" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>3290</v>
+      </c>
       <c r="H20" s="9" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="11" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B22" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C22" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D22" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E22" s="9" t="n">
         <v>1120</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F22" s="9" t="n">
         <v>57.5</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G22" s="9" t="n">
         <v>1350</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H22" s="9" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1435,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1495,12 +1515,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1524,12 +1544,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1553,12 +1573,12 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1567,27 +1587,27 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>71.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1596,27 +1616,27 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>73.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1624,28 +1644,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>82.5</v>
+      <c r="D8" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>495</v>
+        <v>3</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>255</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1653,28 +1673,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>82.5</v>
+      <c r="D9" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>412.5</v>
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>92.8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1682,28 +1702,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>82.5</v>
+      <c r="D10" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>577.5</v>
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1712,22 +1732,22 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>560</v>
+        <v>80</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1756,7 +1776,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1773,19 +1793,19 @@
         <v>50</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>57.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1799,22 +1819,22 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1828,22 +1848,22 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>78.8</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1856,23 +1876,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>80</v>
+      <c r="D16" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>480</v>
+      <c r="F16" s="11" t="n">
+        <v>495</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>92</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1885,23 +1905,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>80</v>
+      <c r="D17" s="9" t="n">
+        <v>82.5</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>480</v>
+        <v>5</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>412.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>92</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1914,28 +1934,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>80</v>
+      <c r="D18" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>480</v>
+        <v>7</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>577.5</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>92</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1944,27 +1964,27 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1973,27 +1993,27 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2002,27 +2022,27 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>64.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2031,27 +2051,27 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>73.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2060,27 +2080,27 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>86</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2092,24 +2112,24 @@
         <v>80</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2118,27 +2138,27 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2147,27 +2167,27 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2176,27 +2196,27 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2205,27 +2225,27 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2233,28 +2253,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>77.5</v>
+      <c r="D29" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>542.5</v>
+        <v>3</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>180</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2262,28 +2282,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
-        <v>77.5</v>
+      <c r="D30" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>465</v>
+        <v>2</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>140</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2291,28 +2311,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>77.5</v>
+      <c r="D31" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>465</v>
+        <v>3</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2320,28 +2340,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n">
-        <v>77.5</v>
+      <c r="D32" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>232.5</v>
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>83.3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2350,22 +2370,22 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2379,22 +2399,22 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2408,22 +2428,22 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2436,23 +2456,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>77.5</v>
+      <c r="D36" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>310</v>
+        <v>3</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>85.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2469,19 +2489,19 @@
         <v>77.5</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>155</v>
+        <v>542.5</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>81.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -2494,260 +2514,260 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>60</v>
+      <c r="D38" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>465</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>67.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>20</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>465</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>25</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>50</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>232.5</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>57.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>525</v>
+        <v>400</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>450</v>
+        <v>195</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>86.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>375</v>
+        <v>4</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>310</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>20</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>155</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>25</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>60</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2756,27 +2776,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>67.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2785,27 +2805,27 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>71.8</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2813,28 +2833,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>72.5</v>
+      <c r="D49" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>507.5</v>
+        <v>3</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>195</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>85.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2842,28 +2862,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
-        <v>72.5</v>
+      <c r="D50" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>580</v>
+        <v>7</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>525</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2871,28 +2891,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>72.5</v>
+      <c r="D51" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>435</v>
+      <c r="F51" s="8" t="n">
+        <v>450</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -2900,23 +2920,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D52" s="11" t="n">
-        <v>62.5</v>
+      <c r="D52" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>750</v>
+        <v>5</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>375</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>81.2</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -2945,7 +2965,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2974,7 +2994,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -2991,19 +3011,19 @@
         <v>60</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>64.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -3020,19 +3040,19 @@
         <v>70</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>560</v>
+        <v>70</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>84</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -3045,23 +3065,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
-        <v>70</v>
+      <c r="D57" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>560</v>
+        <v>7</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>84</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -3074,23 +3094,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n">
-        <v>70</v>
+      <c r="D58" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F58" s="10" t="n">
-        <v>420</v>
+        <v>8</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3103,23 +3123,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
-        <v>80</v>
+      <c r="D59" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>80</v>
+        <v>6</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>82</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -3132,28 +3152,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
-        <v>60</v>
+      <c r="D60" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>480</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>72</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -3177,12 +3197,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3191,27 +3211,27 @@
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F62" s="10" t="n">
         <v>400</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -3220,27 +3240,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>58.8</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3249,27 +3269,27 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>61.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -3278,27 +3298,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>65</v>
+        <v>560</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3310,24 +3330,24 @@
         <v>70</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>78.8</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -3336,27 +3356,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>80.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3365,16 +3385,16 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
@@ -3394,16 +3414,16 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -3423,22 +3443,22 @@
         </is>
       </c>
       <c r="D70" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G70" s="11" t="n">
         <v>50</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G70" s="11" t="n">
-        <v>57.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -3452,22 +3472,22 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>25</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -3481,22 +3501,22 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>48</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -3510,22 +3530,22 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>57.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -3539,22 +3559,22 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>61.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -3567,23 +3587,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="9" t="n">
-        <v>67.5</v>
+      <c r="D75" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>337.5</v>
+        <v>6</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>420</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -3596,23 +3616,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="11" t="n">
-        <v>67.5</v>
+      <c r="D76" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F76" s="11" t="n">
-        <v>472.5</v>
+        <v>3</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>210</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>79.3</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -3625,23 +3645,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>67.5</v>
+      <c r="D77" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E77" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F77" s="9" t="n">
-        <v>270</v>
+      <c r="F77" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>74.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -3654,17 +3674,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D78" s="11" t="n">
-        <v>67.5</v>
+      <c r="D78" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" s="11" t="n">
-        <v>202.5</v>
+        <v>6</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>72.59999999999999</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="79">
@@ -3683,17 +3703,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D79" s="9" t="n">
-        <v>77.5</v>
+      <c r="D79" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="9" t="n">
-        <v>77.5</v>
+        <v>10</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -3713,27 +3733,27 @@
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -3742,27 +3762,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>25</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -3771,27 +3791,27 @@
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -3799,28 +3819,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
-        <v>50</v>
+      <c r="D83" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F83" s="8" t="n">
-        <v>250</v>
+      <c r="F83" s="9" t="n">
+        <v>337.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>56.2</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -3828,28 +3848,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n">
-        <v>65</v>
+      <c r="D84" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3857,28 +3877,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n">
-        <v>65</v>
+      <c r="D85" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>520</v>
+        <v>4</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>78</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -3886,28 +3906,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n">
-        <v>65</v>
+      <c r="D86" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F86" s="10" t="n">
-        <v>455</v>
+        <v>3</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3915,28 +3935,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
-        <v>65</v>
+      <c r="D87" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" s="8" t="n">
-        <v>195</v>
+        <v>1</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -3945,16 +3965,16 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>325</v>
+        <v>480</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -3974,16 +3994,16 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -4003,22 +4023,22 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>76.90000000000001</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -4032,22 +4052,22 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>35</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -4061,22 +4081,22 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>400</v>
+        <v>195</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>50</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -4090,22 +4110,22 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>150</v>
+        <v>520</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -4118,23 +4138,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D94" s="11" t="n">
-        <v>62.5</v>
+      <c r="D94" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F94" s="11" t="n">
-        <v>500</v>
+        <v>7</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>455</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>75</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -4147,23 +4167,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D95" s="9" t="n">
-        <v>62.5</v>
+      <c r="D95" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F95" s="9" t="n">
-        <v>437.5</v>
+        <v>3</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>195</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>73.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -4176,23 +4196,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D96" s="11" t="n">
-        <v>62.5</v>
+      <c r="D96" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F96" s="11" t="n">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>325</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -4205,23 +4225,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n">
-        <v>62.5</v>
+      <c r="D97" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>325</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -4234,17 +4254,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="11" t="n">
-        <v>62.5</v>
+      <c r="D98" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" s="11" t="n">
-        <v>187.5</v>
+        <v>1</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>67.2</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -4263,144 +4283,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
-        <v>72.2</v>
+      <c r="D99" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="9" t="n">
-        <v>72.2</v>
+        <v>10</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E100" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>22.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F103" s="8" t="n">
-        <v>150</v>
+        <v>7</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>437.5</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>53.8</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
@@ -4408,28 +4428,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n">
-        <v>20</v>
+      <c r="D104" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -4437,28 +4457,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
-        <v>40</v>
+      <c r="D105" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F105" s="8" t="n">
-        <v>320</v>
+      <c r="F105" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
@@ -4466,28 +4486,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n">
-        <v>50</v>
+      <c r="D106" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F106" s="10" t="n">
-        <v>250</v>
+        <v>3</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>56.2</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -4495,133 +4515,133 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D107" s="8" t="n">
-        <v>60</v>
+      <c r="D107" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F107" s="8" t="n">
-        <v>480</v>
+        <v>1</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>72</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>72</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="112">
@@ -4641,22 +4661,22 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>71.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -4670,22 +4690,22 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -4699,22 +4719,22 @@
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>48</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -4728,22 +4748,22 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>56.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -4760,24 +4780,24 @@
         <v>60</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4786,27 +4806,27 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
@@ -4815,27 +4835,27 @@
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>56.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -4843,28 +4863,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D119" s="9" t="n">
-        <v>57.5</v>
+      <c r="D119" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>345</v>
+        <v>3</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>210</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -4872,28 +4892,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D120" s="11" t="n">
-        <v>57.5</v>
+      <c r="D120" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F120" s="11" t="n">
-        <v>460</v>
+        <v>1</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4901,28 +4921,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D121" s="9" t="n">
-        <v>57.5</v>
+      <c r="D121" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>345</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -4930,28 +4950,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D122" s="11" t="n">
-        <v>67.5</v>
+      <c r="D122" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F122" s="11" t="n">
-        <v>135</v>
+        <v>8</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4960,27 +4980,27 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>25</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -4989,22 +5009,22 @@
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F124" s="10" t="n">
         <v>240</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
@@ -5018,22 +5038,22 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -5047,22 +5067,22 @@
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>66</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -5075,23 +5095,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n">
-        <v>55</v>
+      <c r="D127" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F127" s="8" t="n">
-        <v>440</v>
+        <v>6</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -5104,23 +5124,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n">
-        <v>55</v>
+      <c r="D128" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>275</v>
+        <v>8</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>61.9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
@@ -5133,249 +5153,249 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D129" s="8" t="n">
-        <v>65</v>
+      <c r="D129" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="8" t="n">
-        <v>65</v>
+        <v>6</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D130" s="10" t="n">
-        <v>10</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F130" s="10" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>11.2</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
         <v>40</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
         <v>50</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E134" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>500</v>
+        <v>275</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>69</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -5395,16 +5415,16 @@
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>67.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="139">
@@ -5424,22 +5444,22 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -5449,26 +5469,26 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F140" s="10" t="n">
         <v>200</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -5478,26 +5498,26 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -5507,26 +5527,26 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -5536,26 +5556,26 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F143" s="9" t="n">
-        <v>315</v>
+        <v>8</v>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -5565,26 +5585,26 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D144" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F144" s="11" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>500</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>60.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -5594,26 +5614,26 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F145" s="9" t="n">
-        <v>420</v>
+        <v>6</v>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -5623,26 +5643,26 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D146" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F146" s="11" t="n">
-        <v>420</v>
+        <v>5</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>63</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -5652,20 +5672,20 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F147" s="9" t="n">
-        <v>315</v>
+        <v>8</v>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>60.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="148">
@@ -5684,28 +5704,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D148" s="11" t="n">
-        <v>62.5</v>
+      <c r="D148" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F148" s="11" t="n">
-        <v>125</v>
+        <v>10</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>65.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
@@ -5714,27 +5734,27 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
@@ -5743,27 +5763,27 @@
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>48</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
@@ -5771,28 +5791,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D151" s="8" t="n">
-        <v>50</v>
+      <c r="D151" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F151" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F151" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
@@ -5800,28 +5820,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n">
-        <v>50</v>
+      <c r="D152" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F152" s="10" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
@@ -5829,28 +5849,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D153" s="8" t="n">
-        <v>50</v>
+      <c r="D153" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F153" s="8" t="n">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>420</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>57.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
@@ -5858,354 +5878,608 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D154" s="10" t="n">
-        <v>50</v>
+      <c r="D154" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E154" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F154" s="10" t="n">
-        <v>400</v>
+      <c r="F154" s="11" t="n">
+        <v>420</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F155" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="G155" s="9" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="G156" s="11" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="E155" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F155" s="8" t="n">
-        <v>180</v>
-      </c>
-      <c r="G155" s="9" t="n">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="13" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G157" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G158" s="11" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="n">
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G159" s="9" t="n">
         <v>60</v>
-      </c>
-      <c r="C159" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="D159" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B160" s="11" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="C160" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="D160" s="11" t="n">
-        <v>5670</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>19</v>
+        <v>400</v>
+      </c>
+      <c r="G160" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B161" s="9" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C161" s="9" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D161" s="9" t="n">
-        <v>3545</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>13</v>
+        <v>300</v>
+      </c>
+      <c r="G161" s="9" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="B162" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C162" s="11" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="D162" s="11" t="n">
-        <v>3980</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>13</v>
+        <v>400</v>
+      </c>
+      <c r="G162" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="B163" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C163" s="9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D163" s="9" t="n">
-        <v>550</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t>2026-W17</t>
-        </is>
-      </c>
-      <c r="B164" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="C164" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="D164" s="11" t="n">
-        <v>5967.2</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" s="10" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>2026-W18</t>
-        </is>
-      </c>
-      <c r="B165" s="9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C165" s="9" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="D165" s="9" t="n">
-        <v>5355</v>
-      </c>
-      <c r="E165" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" s="8" t="n">
-        <v>20</v>
+        <v>180</v>
+      </c>
+      <c r="G163" s="9" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
-        <is>
-          <t>2026-W19</t>
-        </is>
-      </c>
-      <c r="B166" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="C166" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="D166" s="11" t="n">
-        <v>6122.5</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" s="10" t="n">
-        <v>16</v>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="B167" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C167" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="D167" s="9" t="n">
-        <v>2045</v>
+        <v>2200</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="B168" s="11" t="n">
-        <v>77.5</v>
+        <v>62.5</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>4060</v>
+        <v>5670</v>
       </c>
       <c r="E168" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="n">
-        <v>80</v>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="C169" s="9" t="n">
-        <v>86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1600</v>
+        <v>3545</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>2026-W23</t>
-        </is>
-      </c>
-      <c r="B170" s="11" t="n">
-        <v>82.5</v>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>5140</v>
+        <v>3980</v>
       </c>
       <c r="E170" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F170" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>5967.2</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C173" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>5355</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C175" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D176" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C177" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C178" s="11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D178" s="11" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" s="10" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C179" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="8" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A157:G157"/>
+    <mergeCell ref="A165:G165"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$167:$A$179</f>
+              <f>'ベンチプレス'!$A$179:$A$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$167:$C$179</f>
+              <f>'ベンチプレス'!$C$179:$C$192</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>176</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-06-15）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-06-21）</t>
         </is>
       </c>
     </row>
@@ -1151,292 +1151,312 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W24</t>
+          <t>2026-W25</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W23</t>
+          <t>2026-W24</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5140</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>2700</v>
-      </c>
+        <v>1465</v>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>7840</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W23</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>86</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+        <v>5140</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2700</v>
+      </c>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n">
-        <v>1600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="9" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
+      <c r="F15" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>1260</v>
+      </c>
       <c r="H15" s="11" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="9" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
       <c r="H16" s="9" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="11" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="9" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
+      <c r="F19" s="11" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>2540</v>
+      </c>
       <c r="H19" s="11" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="9" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
+      <c r="F21" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>3290</v>
+      </c>
       <c r="H21" s="11" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="9" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B23" s="11" t="n">
         <v>64.5</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C23" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D23" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E23" s="11" t="n">
         <v>1120</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F23" s="11" t="n">
         <v>57.5</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G23" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H23" s="11" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1455,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1515,12 +1535,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1544,12 +1564,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1561,24 +1581,24 @@
         <v>50</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1590,24 +1610,24 @@
         <v>65</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>68.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1616,27 +1636,27 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>82</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1660,12 +1680,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1674,27 +1694,27 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>86</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1703,27 +1723,27 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1732,27 +1752,27 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>82</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1761,27 +1781,27 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>25</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1790,27 +1810,27 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>400</v>
+        <v>490</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>60</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1822,24 +1842,24 @@
         <v>70</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>71.8</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1851,24 +1871,24 @@
         <v>70</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>140</v>
+        <v>420</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>73.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1876,28 +1896,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>82.5</v>
+      <c r="D16" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>495</v>
+        <v>10</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1905,28 +1925,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>82.5</v>
+      <c r="D17" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>412.5</v>
+        <v>8</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>92.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1934,28 +1954,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>82.5</v>
+      <c r="D18" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>577.5</v>
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>130</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1964,27 +1984,27 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>560</v>
+        <v>80</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1993,27 +2013,27 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>25</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2022,27 +2042,27 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>57.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2051,27 +2071,27 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2080,22 +2100,22 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>78.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -2109,22 +2129,22 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2138,22 +2158,22 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2167,27 +2187,27 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>480</v>
+        <v>70</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>92</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2196,27 +2216,27 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>25</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2224,28 +2244,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>50</v>
+      <c r="D28" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>495</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>60</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2253,28 +2273,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
-        <v>60</v>
+      <c r="D29" s="9" t="n">
+        <v>82.5</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>180</v>
+        <v>5</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>412.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>64.5</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2282,28 +2302,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>70</v>
+      <c r="D30" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>140</v>
+        <v>7</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>577.5</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>73.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2312,27 +2332,27 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2341,27 +2361,27 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2370,27 +2390,27 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>69</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2399,27 +2419,27 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -2428,27 +2448,27 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>60</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2457,27 +2477,27 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>195</v>
+        <v>480</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -2485,28 +2505,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>77.5</v>
+      <c r="D37" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>542.5</v>
+        <v>6</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>480</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2514,28 +2534,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
-        <v>77.5</v>
+      <c r="D38" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>465</v>
+      <c r="F38" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2543,28 +2563,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>77.5</v>
+      <c r="D39" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>465</v>
+        <v>10</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2572,28 +2592,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>77.5</v>
+      <c r="D40" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>232.5</v>
+        <v>8</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -2602,27 +2622,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>25</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2631,27 +2651,27 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>60</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2660,27 +2680,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2688,28 +2708,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>77.5</v>
+      <c r="D44" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>310</v>
+        <v>1</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>85.2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -2717,23 +2737,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>77.5</v>
+      <c r="D45" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>155</v>
+        <v>6</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>81.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2747,206 +2767,206 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>67.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>57.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>65</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="8" t="n">
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>542.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F50" s="10" t="n">
-        <v>525</v>
+        <v>6</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>465</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="8" t="n">
-        <v>450</v>
+      <c r="F51" s="9" t="n">
+        <v>465</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>86.2</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <v>375</v>
+        <v>3</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>232.5</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>84.40000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D53" s="8" t="n">
@@ -2965,17 +2985,17 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
@@ -2994,128 +3014,128 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>67.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>70</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>70</v>
+        <v>4</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>310</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>71.8</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>507.5</v>
+        <v>155</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>85.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="n">
-        <v>72.5</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" s="11" t="n">
-        <v>580</v>
+        <v>5</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>87</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -3123,28 +3143,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D59" s="9" t="n">
-        <v>72.5</v>
+      <c r="D59" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F59" s="9" t="n">
-        <v>435</v>
+        <v>10</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3152,28 +3172,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D60" s="11" t="n">
-        <v>62.5</v>
+      <c r="D60" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>750</v>
+        <v>6</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>81.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -3182,27 +3202,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3211,27 +3231,27 @@
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>400</v>
+        <v>525</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>60</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -3240,27 +3260,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>64.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3269,22 +3289,22 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>560</v>
+        <v>375</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>84</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3298,22 +3318,22 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3327,22 +3347,22 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>80.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -3356,22 +3376,22 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>82</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3385,27 +3405,27 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>480</v>
+        <v>70</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3413,28 +3433,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="n">
-        <v>20</v>
+      <c r="D69" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>25</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3442,28 +3462,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n">
-        <v>40</v>
+      <c r="D70" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>400</v>
+        <v>8</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -3471,28 +3491,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n">
-        <v>50</v>
+      <c r="D71" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>350</v>
+        <v>6</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>58.8</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -3500,28 +3520,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n">
-        <v>60</v>
+      <c r="D72" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>61.5</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -3530,27 +3550,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -3559,27 +3579,27 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>78.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3588,27 +3608,27 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>80.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -3620,24 +3640,24 @@
         <v>70</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>210</v>
+        <v>560</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>75.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -3649,24 +3669,24 @@
         <v>70</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -3675,27 +3695,27 @@
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>6</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>57.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -3704,27 +3724,27 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -3733,22 +3753,22 @@
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -3762,22 +3782,22 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>57.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -3791,22 +3811,22 @@
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -3819,23 +3839,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
-        <v>67.5</v>
+      <c r="D83" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>337.5</v>
+        <v>7</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>350</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -3848,23 +3868,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D84" s="11" t="n">
-        <v>67.5</v>
+      <c r="D84" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F84" s="11" t="n">
-        <v>472.5</v>
+        <v>1</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>79.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -3877,23 +3897,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D85" s="9" t="n">
-        <v>67.5</v>
+      <c r="D85" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F85" s="9" t="n">
-        <v>270</v>
+        <v>1</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>74.2</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -3906,23 +3926,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D86" s="11" t="n">
-        <v>67.5</v>
+      <c r="D86" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F86" s="11" t="n">
-        <v>202.5</v>
+        <v>5</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>350</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>72.59999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -3935,23 +3955,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n">
-        <v>77.5</v>
+      <c r="D87" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="9" t="n">
-        <v>77.5</v>
+        <v>6</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>420</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -3965,27 +3985,27 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>480</v>
+        <v>210</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>72</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3994,27 +4014,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -4023,27 +4043,27 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -4052,27 +4072,27 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>56.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -4081,27 +4101,27 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>195</v>
+        <v>320</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -4110,27 +4130,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>78</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -4139,27 +4159,27 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>455</v>
+        <v>60</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -4167,28 +4187,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D95" s="8" t="n">
-        <v>65</v>
+      <c r="D95" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" s="8" t="n">
-        <v>195</v>
+        <v>5</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>337.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -4196,28 +4216,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n">
-        <v>65</v>
+      <c r="D96" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>325</v>
+        <v>7</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -4225,28 +4245,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
-        <v>65</v>
+      <c r="D97" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" s="8" t="n">
-        <v>325</v>
+        <v>4</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -4254,28 +4274,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n">
-        <v>75</v>
+      <c r="D98" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="10" t="n">
-        <v>75</v>
+        <v>3</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>76.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -4283,28 +4303,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
-        <v>28</v>
+      <c r="D99" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <v>280</v>
+        <v>1</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>35</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -4313,22 +4333,22 @@
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -4342,22 +4362,22 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -4370,23 +4390,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D102" s="11" t="n">
-        <v>62.5</v>
+      <c r="D102" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F102" s="11" t="n">
-        <v>500</v>
+        <v>10</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -4399,23 +4419,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D103" s="9" t="n">
-        <v>62.5</v>
+      <c r="D103" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F103" s="9" t="n">
-        <v>437.5</v>
+        <v>5</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>73.40000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -4428,23 +4448,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="11" t="n">
-        <v>62.5</v>
+      <c r="D104" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F104" s="11" t="n">
-        <v>500</v>
+        <v>3</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>75</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -4457,23 +4477,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D105" s="9" t="n">
-        <v>62.5</v>
+      <c r="D105" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F105" s="9" t="n">
-        <v>500</v>
+      <c r="F105" s="8" t="n">
+        <v>520</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -4486,23 +4506,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D106" s="11" t="n">
-        <v>62.5</v>
+      <c r="D106" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" s="11" t="n">
-        <v>187.5</v>
+        <v>7</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>455</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>67.2</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -4515,144 +4535,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D107" s="9" t="n">
-        <v>72.2</v>
+      <c r="D107" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>72.2</v>
+        <v>3</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>195</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>74</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>12.5</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>22.5</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>45</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>53.8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -4661,27 +4681,27 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E112" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -4690,27 +4710,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>48</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -4718,28 +4738,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n">
-        <v>50</v>
+      <c r="D114" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F114" s="10" t="n">
-        <v>250</v>
+        <v>8</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>56.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -4747,28 +4767,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D115" s="8" t="n">
-        <v>60</v>
+      <c r="D115" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F115" s="8" t="n">
-        <v>480</v>
+        <v>7</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>437.5</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -4776,28 +4796,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n">
-        <v>60</v>
+      <c r="D116" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E116" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F116" s="10" t="n">
-        <v>480</v>
+      <c r="F116" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4805,28 +4825,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D117" s="8" t="n">
-        <v>60</v>
+      <c r="D117" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E117" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F117" s="8" t="n">
-        <v>480</v>
+      <c r="F117" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
@@ -4834,28 +4854,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n">
-        <v>60</v>
+      <c r="D118" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F118" s="10" t="n">
-        <v>480</v>
+        <v>3</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>72</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -4863,139 +4883,139 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n">
-        <v>70</v>
+      <c r="D119" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F119" s="8" t="n">
-        <v>210</v>
+        <v>1</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>75.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>71.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
         <v>20</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
         <v>40</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
         <v>50</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -5009,27 +5029,27 @@
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -5038,27 +5058,27 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
@@ -5082,12 +5102,12 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -5095,28 +5115,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D127" s="9" t="n">
-        <v>57.5</v>
+      <c r="D127" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F127" s="9" t="n">
-        <v>345</v>
+        <v>8</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>480</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
@@ -5124,28 +5144,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D128" s="11" t="n">
-        <v>57.5</v>
+      <c r="D128" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E128" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F128" s="11" t="n">
-        <v>460</v>
+      <c r="F128" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -5153,28 +5173,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D129" s="9" t="n">
-        <v>57.5</v>
+      <c r="D129" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>345</v>
+        <v>8</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>480</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -5182,28 +5202,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D130" s="11" t="n">
-        <v>67.5</v>
+      <c r="D130" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F130" s="11" t="n">
-        <v>135</v>
+        <v>8</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>480</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
@@ -5212,27 +5232,27 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>25</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -5241,27 +5261,27 @@
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>46</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
@@ -5270,27 +5290,27 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
@@ -5299,27 +5319,27 @@
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E134" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>440</v>
+        <v>320</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
@@ -5328,27 +5348,27 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>66</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
@@ -5357,22 +5377,22 @@
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>61.9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -5386,317 +5406,317 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>11.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D139" s="8" t="n">
-        <v>30</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F139" s="8" t="n">
-        <v>240</v>
+        <v>6</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F140" s="10" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F141" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>60</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>2</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>60</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>62.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>69</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>67.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E147" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>320</v>
+        <v>440</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
@@ -5705,27 +5725,27 @@
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>25</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
@@ -5734,22 +5754,22 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>240</v>
+        <v>65</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>46</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -5759,26 +5779,26 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E150" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F150" s="10" t="n">
-        <v>150</v>
-      </c>
       <c r="G150" s="11" t="n">
-        <v>53.8</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -5788,26 +5808,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F151" s="9" t="n">
-        <v>315</v>
+        <v>8</v>
+      </c>
+      <c r="F151" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>60.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -5817,26 +5837,26 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F152" s="11" t="n">
-        <v>315</v>
+        <v>5</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>60.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -5846,26 +5866,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E153" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F153" s="9" t="n">
-        <v>420</v>
+      <c r="F153" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -5875,26 +5895,26 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D154" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E154" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F154" s="11" t="n">
-        <v>420</v>
+      <c r="F154" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -5904,26 +5924,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F155" s="9" t="n">
-        <v>315</v>
+        <v>8</v>
+      </c>
+      <c r="F155" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
@@ -5933,118 +5953,118 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D156" s="11" t="n">
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G156" s="11" t="n">
         <v>62.5</v>
-      </c>
-      <c r="E156" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="G156" s="11" t="n">
-        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>48</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E159" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
@@ -6053,27 +6073,27 @@
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
@@ -6082,27 +6102,27 @@
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E161" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>57.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
@@ -6114,24 +6134,24 @@
         <v>50</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
@@ -6139,347 +6159,717 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D163" s="8" t="n">
-        <v>60</v>
+      <c r="D163" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F163" s="8" t="n">
-        <v>180</v>
+        <v>6</v>
+      </c>
+      <c r="F163" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="13" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="G164" s="11" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>420</v>
+      </c>
+      <c r="G165" s="9" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="G166" s="11" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>64.5</v>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>2200</v>
+        <v>52.5</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F167" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="G167" s="9" t="n">
+        <v>60.4</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B168" s="11" t="n">
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="n">
         <v>62.5</v>
-      </c>
-      <c r="C168" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="D168" s="11" t="n">
-        <v>5670</v>
       </c>
       <c r="E168" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F168" s="10" t="n">
-        <v>19</v>
+      <c r="F168" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="G168" s="11" t="n">
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C169" s="9" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D169" s="9" t="n">
-        <v>3545</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>13</v>
+        <v>200</v>
+      </c>
+      <c r="G169" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="B170" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C170" s="11" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="D170" s="11" t="n">
-        <v>3980</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>13</v>
+        <v>320</v>
+      </c>
+      <c r="G170" s="11" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="n">
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="C171" s="9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D171" s="9" t="n">
-        <v>550</v>
-      </c>
       <c r="E171" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>4</v>
+        <v>400</v>
+      </c>
+      <c r="G171" s="9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>2026-W17</t>
-        </is>
-      </c>
-      <c r="B172" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="C172" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="D172" s="11" t="n">
-        <v>5967.2</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>19</v>
+        <v>400</v>
+      </c>
+      <c r="G172" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
-        </is>
-      </c>
-      <c r="B173" s="9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C173" s="9" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="D173" s="9" t="n">
-        <v>5355</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>20</v>
+        <v>300</v>
+      </c>
+      <c r="G173" s="9" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
-        </is>
-      </c>
-      <c r="B174" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="C174" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="D174" s="11" t="n">
-        <v>6122.5</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>16</v>
+        <v>400</v>
+      </c>
+      <c r="G174" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="C175" s="9" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="D175" s="9" t="n">
-        <v>2045</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>2026-W21</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C176" s="11" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="D176" s="11" t="n">
-        <v>4060</v>
-      </c>
-      <c r="E176" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" s="10" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t>2026-W22</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="C177" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="D177" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E177" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F177" s="8" t="n">
-        <v>7</v>
+        <v>180</v>
+      </c>
+      <c r="G175" s="9" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="10" t="inlineStr">
-        <is>
-          <t>2026-W23</t>
-        </is>
-      </c>
-      <c r="B178" s="11" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="D178" s="11" t="n">
-        <v>5140</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" s="10" t="n">
-        <v>15</v>
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>2026-W24</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="B179" s="8" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C179" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>1465</v>
+        <v>2200</v>
       </c>
       <c r="E179" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F179" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C180" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="D180" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C181" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>3545</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D182" s="11" t="n">
+        <v>3980</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C183" s="9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C184" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D184" s="11" t="n">
+        <v>5967.2</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C185" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>5355</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="D186" s="11" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C187" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D188" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C189" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C190" s="11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D190" s="11" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" s="10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="8" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="C192" s="11" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D192" s="11" t="n">
+        <v>3410</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A165:G165"/>
+    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-06-21）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-06-28）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-06-28）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-07-05）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-07-05）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-07-12）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-07-12）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-07-19）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-07-19）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-07-26）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$179:$A$192</f>
+              <f>'ベンチプレス'!$A$185:$A$199</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$179:$C$192</f>
+              <f>'ベンチプレス'!$C$185:$C$199</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>176</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-07-26）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-08-02）</t>
         </is>
       </c>
     </row>
@@ -1151,312 +1151,332 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W25</t>
+          <t>2026-W31</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>3410</v>
+        <v>1720</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>3410</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W24</t>
+          <t>2026-W25</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W23</t>
+          <t>2026-W24</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>96.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>5140</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>2700</v>
-      </c>
+        <v>1465</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n">
-        <v>7840</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W23</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>86</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
+        <v>5140</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>2700</v>
+      </c>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>1600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="9" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1260</v>
+      </c>
       <c r="H16" s="9" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
-      <c r="F17" s="11" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
       <c r="H17" s="11" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="11" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>2540</v>
+      </c>
       <c r="H20" s="9" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
-      <c r="F21" s="11" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
       <c r="H21" s="11" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="F22" s="9" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>3290</v>
+      </c>
       <c r="H22" s="9" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="11" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B24" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C24" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D24" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E24" s="9" t="n">
         <v>1120</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>57.5</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G24" s="9" t="n">
         <v>1350</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H24" s="9" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1475,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1535,12 +1555,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1564,12 +1584,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1578,27 +1598,27 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>58.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1607,27 +1627,27 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1636,27 +1656,27 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>78.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1665,27 +1685,27 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>255</v>
+        <v>420</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1694,22 +1714,22 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>89.2</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -1738,7 +1758,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1767,7 +1787,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1781,22 +1801,22 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>75.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1810,22 +1830,22 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>490</v>
+        <v>150</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>82.2</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1839,22 +1859,22 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>420</v>
+        <v>255</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>80.5</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1868,27 +1888,27 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>80.5</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1912,12 +1932,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1929,24 +1949,24 @@
         <v>50</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1955,27 +1975,27 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>68.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1984,27 +2004,27 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2013,27 +2033,27 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>255</v>
+        <v>420</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2042,16 +2062,16 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>86</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="22">
@@ -2071,16 +2091,16 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -2100,27 +2120,27 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2129,27 +2149,27 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>25</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2158,27 +2178,27 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2187,27 +2207,27 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>71.8</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2216,27 +2236,27 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>73.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2244,28 +2264,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>82.5</v>
+      <c r="D28" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>495</v>
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2273,17 +2293,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>82.5</v>
+      <c r="D29" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>412.5</v>
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>92.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
@@ -2302,17 +2322,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
-        <v>82.5</v>
+      <c r="D30" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>577.5</v>
+        <v>10</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -2332,22 +2352,22 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>560</v>
+        <v>400</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -2361,22 +2381,22 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>25</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2390,22 +2410,22 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>57.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2418,23 +2438,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>65</v>
+      <c r="D34" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>195</v>
+        <v>6</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>495</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2447,23 +2467,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
-        <v>75</v>
+      <c r="D35" s="9" t="n">
+        <v>82.5</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>150</v>
+        <v>5</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>412.5</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>78.8</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2476,23 +2496,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>80</v>
+      <c r="D36" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>480</v>
+        <v>7</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>577.5</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>92</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2506,16 +2526,16 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
@@ -2535,27 +2555,27 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2564,27 +2584,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>25</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2593,27 +2613,27 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>400</v>
+        <v>195</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>60</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -2622,27 +2642,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>64.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2651,27 +2671,27 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>140</v>
+        <v>480</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>73.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2683,24 +2703,24 @@
         <v>80</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2712,13 +2732,13 @@
         <v>80</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
@@ -2738,27 +2758,27 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2767,27 +2787,27 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2796,27 +2816,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>60</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2825,27 +2845,27 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2853,28 +2873,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>77.5</v>
+      <c r="D49" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>542.5</v>
+        <v>3</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2882,28 +2902,28 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
-        <v>77.5</v>
+      <c r="D50" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>465</v>
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2911,17 +2931,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>77.5</v>
+      <c r="D51" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>465</v>
+      <c r="F51" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52">
@@ -2940,23 +2960,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D52" s="11" t="n">
-        <v>77.5</v>
+      <c r="D52" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>232.5</v>
+        <v>10</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>83.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -2970,22 +2990,22 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2999,22 +3019,22 @@
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>400</v>
+        <v>195</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>60</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -3027,23 +3047,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
-        <v>65</v>
+      <c r="D55" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>542.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -3060,19 +3080,19 @@
         <v>77.5</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>310</v>
+        <v>465</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>85.2</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -3089,19 +3109,19 @@
         <v>77.5</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>81.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -3114,33 +3134,33 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n">
-        <v>60</v>
+      <c r="D58" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" s="10" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>232.5</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>67.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
@@ -3159,46 +3179,46 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>57.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
@@ -3217,99 +3237,99 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>525</v>
+        <v>4</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>310</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>75</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" s="8" t="n">
-        <v>450</v>
+        <v>2</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>155</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>86.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>84.40000000000001</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -3333,12 +3353,12 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3350,24 +3370,24 @@
         <v>50</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>60</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -3376,27 +3396,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>67.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3405,27 +3425,27 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>70</v>
+        <v>525</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>71.8</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3433,28 +3453,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n">
-        <v>72.5</v>
+      <c r="D69" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>507.5</v>
+        <v>6</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>450</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>85.2</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3462,17 +3482,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D70" s="11" t="n">
-        <v>72.5</v>
+      <c r="D70" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>580</v>
+        <v>5</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>375</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>87</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3491,17 +3511,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D71" s="9" t="n">
-        <v>72.5</v>
+      <c r="D71" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>435</v>
+        <v>10</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
@@ -3520,23 +3540,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D72" s="11" t="n">
-        <v>62.5</v>
+      <c r="D72" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>750</v>
+        <v>8</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>81.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -3550,22 +3570,22 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>25</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -3579,22 +3599,22 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>60</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -3607,23 +3627,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
-        <v>60</v>
+      <c r="D75" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>180</v>
+        <v>7</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>64.5</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -3636,23 +3656,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
-        <v>70</v>
+      <c r="D76" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F76" s="10" t="n">
-        <v>560</v>
+      <c r="F76" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -3665,23 +3685,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
-        <v>70</v>
+      <c r="D77" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>560</v>
+        <v>6</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>84</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -3694,17 +3714,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n">
-        <v>70</v>
+      <c r="D78" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F78" s="10" t="n">
-        <v>420</v>
+        <v>12</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>80.5</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="79">
@@ -3724,16 +3744,16 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -3753,27 +3773,27 @@
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -3782,27 +3802,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>25</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -3811,27 +3831,27 @@
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -3840,27 +3860,27 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>58.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -3869,27 +3889,27 @@
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>61.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3898,27 +3918,27 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -3927,16 +3947,16 @@
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>78.8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87">
@@ -3956,16 +3976,16 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>80.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -3985,16 +4005,16 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>75.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -4014,16 +4034,16 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>77</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="90">
@@ -4043,22 +4063,22 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>57.5</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -4072,22 +4092,22 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>25</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -4101,22 +4121,22 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>48</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -4130,22 +4150,22 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E93" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>57.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -4159,22 +4179,22 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>61.5</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -4187,23 +4207,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D95" s="9" t="n">
-        <v>67.5</v>
+      <c r="D95" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F95" s="9" t="n">
-        <v>337.5</v>
+        <v>4</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -4216,17 +4236,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D96" s="11" t="n">
-        <v>67.5</v>
+      <c r="D96" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F96" s="11" t="n">
-        <v>472.5</v>
+        <v>6</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>79.3</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="97">
@@ -4245,17 +4265,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n">
-        <v>67.5</v>
+      <c r="D97" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>270</v>
+        <v>10</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>74.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98">
@@ -4274,17 +4294,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D98" s="11" t="n">
-        <v>67.5</v>
+      <c r="D98" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" s="11" t="n">
-        <v>202.5</v>
+        <v>8</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>72.59999999999999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="99">
@@ -4303,17 +4323,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
-        <v>77.5</v>
+      <c r="D99" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="9" t="n">
-        <v>77.5</v>
+        <v>6</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="100">
@@ -4336,24 +4356,24 @@
         <v>60</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>480</v>
+        <v>60</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>72</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -4361,28 +4381,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
-        <v>20</v>
+      <c r="D101" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F101" s="8" t="n">
-        <v>200</v>
+        <v>5</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>337.5</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>25</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
@@ -4390,28 +4410,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n">
-        <v>40</v>
+      <c r="D102" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>400</v>
+        <v>7</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>50</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -4419,28 +4439,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D103" s="8" t="n">
-        <v>50</v>
+      <c r="D103" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F103" s="8" t="n">
-        <v>250</v>
+        <v>4</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>56.2</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
@@ -4448,28 +4468,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n">
-        <v>65</v>
+      <c r="D104" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F104" s="10" t="n">
-        <v>195</v>
+      <c r="F104" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -4477,28 +4497,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
-        <v>65</v>
+      <c r="D105" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F105" s="8" t="n">
-        <v>520</v>
+        <v>1</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>78</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
@@ -4507,16 +4527,16 @@
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107">
@@ -4536,16 +4556,16 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
@@ -4565,16 +4585,16 @@
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109">
@@ -4594,16 +4614,16 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="110">
@@ -4623,22 +4643,22 @@
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>76.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -4652,22 +4672,22 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>280</v>
+        <v>520</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -4681,22 +4701,22 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>400</v>
+        <v>455</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>50</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -4710,22 +4730,22 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E113" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>53.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -4738,23 +4758,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D114" s="11" t="n">
-        <v>62.5</v>
+      <c r="D114" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F114" s="11" t="n">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>325</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -4767,23 +4787,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D115" s="9" t="n">
-        <v>62.5</v>
+      <c r="D115" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F115" s="9" t="n">
-        <v>437.5</v>
+        <v>5</v>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>325</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>73.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -4796,17 +4816,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D116" s="11" t="n">
-        <v>62.5</v>
+      <c r="D116" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" s="11" t="n">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -4825,17 +4845,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D117" s="9" t="n">
-        <v>62.5</v>
+      <c r="D117" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F117" s="9" t="n">
-        <v>500</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118">
@@ -4854,17 +4874,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D118" s="11" t="n">
-        <v>62.5</v>
+      <c r="D118" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F118" s="11" t="n">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>67.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119">
@@ -4883,144 +4903,144 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D119" s="9" t="n">
-        <v>72.2</v>
+      <c r="D119" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>72.2</v>
+        <v>3</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>150</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>74</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="n">
-        <v>10</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F120" s="10" t="n">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="n">
-        <v>20</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>437.5</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>22.5</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F123" s="8" t="n">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -5028,28 +5048,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n">
-        <v>20</v>
+      <c r="D124" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F124" s="10" t="n">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>25</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -5057,133 +5077,133 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n">
-        <v>40</v>
+      <c r="D125" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F125" s="8" t="n">
-        <v>320</v>
+        <v>1</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>56.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>72</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="130">
@@ -5203,16 +5223,16 @@
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131">
@@ -5232,16 +5252,16 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>75.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="132">
@@ -5261,22 +5281,22 @@
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>71.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -5290,22 +5310,22 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -5319,22 +5339,22 @@
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E134" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -5348,22 +5368,22 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>56.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -5380,24 +5400,24 @@
         <v>60</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -5406,27 +5426,27 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>25</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
@@ -5435,27 +5455,27 @@
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>56.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
@@ -5463,28 +5483,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D139" s="9" t="n">
-        <v>57.5</v>
+      <c r="D139" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F139" s="9" t="n">
-        <v>345</v>
+        <v>10</v>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
@@ -5492,28 +5512,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D140" s="11" t="n">
-        <v>57.5</v>
+      <c r="D140" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E140" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F140" s="11" t="n">
-        <v>460</v>
+      <c r="F140" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -5521,28 +5541,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D141" s="9" t="n">
-        <v>57.5</v>
+      <c r="D141" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F141" s="9" t="n">
-        <v>345</v>
+        <v>5</v>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
@@ -5550,23 +5570,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D142" s="11" t="n">
-        <v>67.5</v>
+      <c r="D142" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F142" s="11" t="n">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>240</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -5595,7 +5615,7 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -5609,22 +5629,22 @@
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>46</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -5637,23 +5657,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D145" s="8" t="n">
-        <v>50</v>
+      <c r="D145" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F145" s="8" t="n">
-        <v>150</v>
+        <v>6</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>53.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -5666,23 +5686,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D146" s="10" t="n">
-        <v>55</v>
+      <c r="D146" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E146" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F146" s="10" t="n">
-        <v>440</v>
+      <c r="F146" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -5695,23 +5715,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D147" s="8" t="n">
-        <v>55</v>
+      <c r="D147" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F147" s="8" t="n">
-        <v>440</v>
+        <v>6</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -5724,17 +5744,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D148" s="10" t="n">
-        <v>55</v>
+      <c r="D148" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F148" s="10" t="n">
-        <v>275</v>
+        <v>2</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>61.9</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -5754,190 +5774,190 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>11.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>36</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>200</v>
+        <v>440</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E153" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>60</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -5957,16 +5977,16 @@
         </is>
       </c>
       <c r="D156" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F156" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E156" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F156" s="10" t="n">
-        <v>500</v>
-      </c>
       <c r="G156" s="11" t="n">
-        <v>62.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="157">
@@ -5986,16 +6006,16 @@
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="158">
@@ -6015,16 +6035,16 @@
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E158" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>67.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="159">
@@ -6044,22 +6064,22 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E159" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -6069,26 +6089,26 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -6098,26 +6118,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
@@ -6127,26 +6147,26 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>53.8</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -6156,26 +6176,26 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D163" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E163" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F163" s="9" t="n">
-        <v>315</v>
+      <c r="F163" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>60.4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -6185,26 +6205,26 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F164" s="11" t="n">
-        <v>315</v>
+        <v>5</v>
+      </c>
+      <c r="F164" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G164" s="11" t="n">
-        <v>60.4</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -6214,20 +6234,20 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E165" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F165" s="9" t="n">
-        <v>420</v>
+      <c r="F165" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="166">
@@ -6246,17 +6266,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D166" s="11" t="n">
-        <v>52.5</v>
+      <c r="D166" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F166" s="11" t="n">
-        <v>420</v>
+        <v>10</v>
+      </c>
+      <c r="F166" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G166" s="11" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167">
@@ -6275,17 +6295,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D167" s="9" t="n">
-        <v>52.5</v>
+      <c r="D167" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F167" s="9" t="n">
-        <v>315</v>
+      <c r="F167" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G167" s="9" t="n">
-        <v>60.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="168">
@@ -6304,28 +6324,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D168" s="11" t="n">
-        <v>62.5</v>
+      <c r="D168" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" s="11" t="n">
-        <v>125</v>
+        <v>3</v>
+      </c>
+      <c r="F168" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="G168" s="11" t="n">
-        <v>65.59999999999999</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -6333,28 +6353,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D169" s="8" t="n">
-        <v>20</v>
+      <c r="D169" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F169" s="8" t="n">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="F169" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>25</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
@@ -6362,28 +6382,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D170" s="10" t="n">
-        <v>40</v>
+      <c r="D170" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F170" s="10" t="n">
-        <v>320</v>
+        <v>6</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="G170" s="11" t="n">
-        <v>48</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
@@ -6391,28 +6411,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n">
-        <v>50</v>
+      <c r="D171" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E171" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F171" s="8" t="n">
-        <v>400</v>
+      <c r="F171" s="9" t="n">
+        <v>420</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
@@ -6420,28 +6440,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D172" s="10" t="n">
-        <v>50</v>
+      <c r="D172" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E172" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F172" s="10" t="n">
-        <v>400</v>
+      <c r="F172" s="11" t="n">
+        <v>420</v>
       </c>
       <c r="G172" s="11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
@@ -6449,28 +6469,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D173" s="8" t="n">
-        <v>50</v>
+      <c r="D173" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E173" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F173" s="8" t="n">
-        <v>300</v>
+      <c r="F173" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>57.5</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
@@ -6478,17 +6498,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D174" s="10" t="n">
-        <v>50</v>
+      <c r="D174" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F174" s="10" t="n">
-        <v>400</v>
+        <v>2</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>125</v>
       </c>
       <c r="G174" s="11" t="n">
-        <v>60</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -6508,269 +6528,311 @@
         </is>
       </c>
       <c r="D175" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F175" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G175" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F176" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="G176" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F177" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G177" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E175" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F175" s="8" t="n">
-        <v>180</v>
-      </c>
-      <c r="G175" s="9" t="n">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="13" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
-      </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F178" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G178" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C179" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="D179" s="9" t="n">
-        <v>2200</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>7</v>
+        <v>300</v>
+      </c>
+      <c r="G179" s="9" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B180" s="11" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="C180" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="D180" s="11" t="n">
-        <v>5670</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>19</v>
+        <v>400</v>
+      </c>
+      <c r="G180" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B181" s="9" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C181" s="9" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D181" s="9" t="n">
-        <v>3545</v>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="B182" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C182" s="11" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="D182" s="11" t="n">
-        <v>3980</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F182" s="10" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C183" s="9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D183" s="9" t="n">
-        <v>550</v>
-      </c>
-      <c r="E183" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" s="8" t="n">
-        <v>4</v>
+        <v>180</v>
+      </c>
+      <c r="G181" s="9" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>2026-W17</t>
-        </is>
-      </c>
-      <c r="B184" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="C184" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="D184" s="11" t="n">
-        <v>5967.2</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F184" s="10" t="n">
-        <v>19</v>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="n">
-        <v>77.5</v>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="C185" s="9" t="n">
-        <v>80.5</v>
+        <v>64.5</v>
       </c>
       <c r="D185" s="9" t="n">
-        <v>5355</v>
+        <v>2200</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
-        </is>
-      </c>
-      <c r="B186" s="10" t="n">
-        <v>80</v>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>6122.5</v>
+        <v>5670</v>
       </c>
       <c r="E186" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="n">
-        <v>75</v>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="C187" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D187" s="9" t="n">
-        <v>2045</v>
+        <v>3545</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
-        </is>
-      </c>
-      <c r="B188" s="11" t="n">
-        <v>77.5</v>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B188" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>4060</v>
+        <v>3980</v>
       </c>
       <c r="E188" s="10" t="n">
         <v>2</v>
@@ -6782,94 +6844,248 @@
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B189" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C189" s="9" t="n">
-        <v>86</v>
+        <v>53.8</v>
       </c>
       <c r="D189" s="9" t="n">
-        <v>1600</v>
+        <v>550</v>
       </c>
       <c r="E189" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>2026-W23</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="n">
-        <v>82.5</v>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>5140</v>
+        <v>5967.2</v>
       </c>
       <c r="E190" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>2026-W24</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="n">
-        <v>85</v>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="C191" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D191" s="9" t="n">
-        <v>1465</v>
+        <v>5355</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>2026-W25</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B192" s="10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>3410</v>
+        <v>6122.5</v>
       </c>
       <c r="E192" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F192" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C193" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D194" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F194" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C195" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C196" s="11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D196" s="11" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F196" s="10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C197" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="C198" s="11" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D198" s="11" t="n">
+        <v>3410</v>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F198" s="10" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>2026-W31</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C199" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A177:G177"/>
+    <mergeCell ref="A183:G183"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-08-02）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-08-09）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-08-09）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-08-16）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-08-16）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-08-23）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ベンチプレス'!$A$185:$A$199</f>
+              <f>'ベンチプレス'!$A$189:$A$204</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ベンチプレス'!$C$185:$C$199</f>
+              <f>'ベンチプレス'!$C$189:$C$204</f>
             </numRef>
           </val>
         </ser>
@@ -638,7 +638,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>182</row>
+      <row>186</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="4320000"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-08-23）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-08-30）</t>
         </is>
       </c>
     </row>
@@ -1151,332 +1151,352 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-W31</t>
+          <t>2026-W35</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>80.5</v>
+        <v>64.5</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1720</v>
+        <v>722</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="9" t="n">
-        <v>1720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-W25</t>
+          <t>2026-W31</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3410</v>
+        <v>1720</v>
       </c>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>3410</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-W24</t>
+          <t>2026-W25</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n">
-        <v>1465</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-W23</t>
+          <t>2026-W24</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5140</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>2700</v>
-      </c>
+        <v>1465</v>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>7840</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
+          <t>2026-W23</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>86</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
+        <v>5140</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2700</v>
+      </c>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="9" t="n">
-        <v>1600</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>4060</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W21</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2045</v>
+        <v>4060</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>1260</v>
-      </c>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
       <c r="H16" s="9" t="n">
-        <v>3305</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>6122.5</v>
+        <v>2045</v>
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="F17" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>1260</v>
+      </c>
       <c r="H17" s="11" t="n">
-        <v>6122.5</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W19</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>80.5</v>
+        <v>87</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>5355</v>
+        <v>6122.5</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>1070</v>
-      </c>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n">
-        <v>6425</v>
+        <v>6122.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5967.2</v>
+        <v>5355</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="11" t="n">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>2132.5</v>
+        <v>1070</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>8099.7</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>53.8</v>
+        <v>78</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>550</v>
+        <v>5967.2</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="9" t="n">
-        <v>86.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2540</v>
+        <v>2132.5</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>3090</v>
+        <v>8099.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>75.2</v>
+        <v>53.8</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3980</v>
+        <v>550</v>
       </c>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
+      <c r="F21" s="11" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>2540</v>
+      </c>
       <c r="H21" s="11" t="n">
-        <v>3980</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>3545</v>
+        <v>3980</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>3290</v>
-      </c>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n">
-        <v>6835</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>5670</v>
+        <v>3545</v>
       </c>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
+      <c r="F23" s="11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>3290</v>
+      </c>
       <c r="H23" s="11" t="n">
-        <v>5670</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>5670</v>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="9" t="n">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
           <t>2026-W12</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B25" s="11" t="n">
         <v>64.5</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C25" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D25" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E25" s="11" t="n">
         <v>1120</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F25" s="11" t="n">
         <v>57.5</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G25" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H25" s="11" t="n">
         <v>4670</v>
       </c>
     </row>
@@ -1495,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1555,12 +1575,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1584,12 +1604,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1598,27 +1618,27 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1630,24 +1650,24 @@
         <v>50</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1659,13 +1679,13 @@
         <v>60</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>67.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="8">
@@ -1685,16 +1705,16 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>80.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -1714,27 +1734,27 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>78.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1743,27 +1763,27 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>25</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1772,27 +1792,27 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>58.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1801,27 +1821,27 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>195</v>
+        <v>420</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1830,13 +1850,13 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>78.8</v>
@@ -1859,16 +1879,16 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1888,22 +1908,22 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>89.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1917,22 +1937,22 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1946,22 +1966,22 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>58.8</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1975,22 +1995,22 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>75.2</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2004,16 +2024,16 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>490</v>
+        <v>170</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>82.2</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="20">
@@ -2033,16 +2053,16 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>80.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -2062,27 +2082,27 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>80.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2091,27 +2111,27 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>25</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2120,27 +2140,27 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>400</v>
+        <v>490</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>60</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2149,27 +2169,27 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>130</v>
+        <v>420</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>68.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2178,16 +2198,16 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>82</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="26">
@@ -2207,16 +2227,16 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -2236,16 +2256,16 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
@@ -2265,16 +2285,16 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>82</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="29">
@@ -2309,12 +2329,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2323,27 +2343,27 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>25</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2352,27 +2372,27 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2381,27 +2401,27 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>71.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2410,16 +2430,16 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>73.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
@@ -2438,17 +2458,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D34" s="11" t="n">
-        <v>82.5</v>
+      <c r="D34" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>495</v>
+        <v>10</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -2467,17 +2487,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>82.5</v>
+      <c r="D35" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>412.5</v>
+        <v>8</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>92.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
@@ -2496,17 +2516,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>82.5</v>
+      <c r="D36" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>577.5</v>
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2549,19 @@
         <v>70</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>560</v>
+        <v>140</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>84</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -2554,23 +2574,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>20</v>
+      <c r="D38" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>495</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>25</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -2583,23 +2603,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
-        <v>50</v>
+      <c r="D39" s="9" t="n">
+        <v>82.5</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>412.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>57.5</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -2612,23 +2632,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>65</v>
+      <c r="D40" s="11" t="n">
+        <v>82.5</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>577.5</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -2642,16 +2662,16 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>150</v>
+        <v>560</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>78.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
@@ -2671,16 +2691,16 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -2700,16 +2720,16 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>92</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="44">
@@ -2729,27 +2749,27 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>480</v>
+        <v>195</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>92</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -2758,27 +2778,27 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>25</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2787,27 +2807,27 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2816,27 +2836,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>64.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2845,16 +2865,16 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>140</v>
+        <v>480</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>73.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
@@ -2874,16 +2894,16 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2903,16 +2923,16 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
@@ -2935,24 +2955,24 @@
         <v>60</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>69</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -2961,27 +2981,27 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>25</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2990,27 +3010,27 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3019,27 +3039,27 @@
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -3047,17 +3067,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D55" s="9" t="n">
-        <v>77.5</v>
+      <c r="D55" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>542.5</v>
+        <v>6</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>91.09999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
@@ -3076,17 +3096,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D56" s="11" t="n">
-        <v>77.5</v>
+      <c r="D56" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F56" s="11" t="n">
-        <v>465</v>
+        <v>10</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -3105,17 +3125,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>77.5</v>
+      <c r="D57" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F57" s="9" t="n">
-        <v>465</v>
+        <v>8</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>400</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
@@ -3134,23 +3154,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D58" s="11" t="n">
-        <v>77.5</v>
+      <c r="D58" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="11" t="n">
-        <v>232.5</v>
+      <c r="F58" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>83.3</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3163,23 +3183,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
-        <v>20</v>
+      <c r="D59" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>542.5</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>25</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -3192,23 +3212,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
-        <v>50</v>
+      <c r="D60" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>465</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>60</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3221,23 +3241,23 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
-        <v>65</v>
+      <c r="D61" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>195</v>
+        <v>6</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>465</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3254,13 +3274,13 @@
         <v>77.5</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>310</v>
+        <v>232.5</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="63">
@@ -3279,17 +3299,17 @@
           <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
-      <c r="D63" s="9" t="n">
-        <v>77.5</v>
+      <c r="D63" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>155</v>
+        <v>10</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>81.40000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
@@ -3309,132 +3329,132 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G64" s="11" t="n">
         <v>60</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G64" s="11" t="n">
-        <v>67.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>50</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>310</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>57.5</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>65</v>
+          <t>ベンチプレス　（バーベル）</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>195</v>
+        <v>2</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>155</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>ベンチプレス　（バーベル）</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="69">
@@ -3454,16 +3474,16 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>86.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -3483,27 +3503,27 @@
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>84.40000000000001</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -3512,27 +3532,27 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -3541,27 +3561,27 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>525</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>60</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -3570,27 +3590,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>67.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -3599,16 +3619,16 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>70</v>
+        <v>375</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>71.8</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3627,17 +3647,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D75" s="9" t="n">
-        <v>72.5</v>
+      <c r="D75" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>507.5</v>
+        <v>10</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>85.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -3656,17 +3676,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D76" s="11" t="n">
-        <v>72.5</v>
+      <c r="D76" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F76" s="11" t="n">
-        <v>580</v>
+      <c r="F76" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77">
@@ -3685,17 +3705,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>72.5</v>
+      <c r="D77" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F77" s="9" t="n">
-        <v>435</v>
+        <v>5</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="78">
@@ -3714,23 +3734,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D78" s="11" t="n">
-        <v>62.5</v>
+      <c r="D78" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F78" s="11" t="n">
-        <v>750</v>
+        <v>1</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>70</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>81.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -3743,23 +3763,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n">
-        <v>20</v>
+      <c r="D79" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>507.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>25</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -3772,23 +3792,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n">
-        <v>50</v>
+      <c r="D80" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F80" s="10" t="n">
-        <v>400</v>
+      <c r="F80" s="11" t="n">
+        <v>580</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -3801,23 +3821,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n">
-        <v>60</v>
+      <c r="D81" s="9" t="n">
+        <v>72.5</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>180</v>
+        <v>6</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>435</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>64.5</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -3830,17 +3850,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n">
-        <v>70</v>
+      <c r="D82" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F82" s="10" t="n">
-        <v>560</v>
+        <v>12</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>750</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>84</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="83">
@@ -3860,16 +3880,16 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
@@ -3889,16 +3909,16 @@
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>80.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -3918,16 +3938,16 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>82</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="86">
@@ -3947,27 +3967,27 @@
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3976,27 +3996,27 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -4005,27 +4025,27 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>50</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -4034,27 +4054,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>58.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -4066,13 +4086,13 @@
         <v>60</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>61.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91">
@@ -4092,16 +4112,16 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -4121,16 +4141,16 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>78.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -4150,16 +4170,16 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>80.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="94">
@@ -4179,16 +4199,16 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>75.2</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="95">
@@ -4208,16 +4228,16 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>280</v>
+        <v>65</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>77</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -4237,22 +4257,22 @@
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>57.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -4266,22 +4286,22 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>25</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -4295,22 +4315,22 @@
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>48</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -4324,22 +4344,22 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>57.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -4353,16 +4373,16 @@
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>61.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="101">
@@ -4381,17 +4401,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D101" s="9" t="n">
-        <v>67.5</v>
+      <c r="D101" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F101" s="9" t="n">
-        <v>337.5</v>
+        <v>10</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -4410,17 +4430,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D102" s="11" t="n">
-        <v>67.5</v>
+      <c r="D102" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F102" s="11" t="n">
-        <v>472.5</v>
+        <v>8</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>79.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103">
@@ -4439,17 +4459,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D103" s="9" t="n">
-        <v>67.5</v>
+      <c r="D103" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F103" s="9" t="n">
-        <v>270</v>
+        <v>6</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>74.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="104">
@@ -4468,17 +4488,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D104" s="11" t="n">
-        <v>67.5</v>
+      <c r="D104" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F104" s="11" t="n">
-        <v>202.5</v>
+        <v>1</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>72.59999999999999</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="105">
@@ -4498,16 +4518,16 @@
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>77.5</v>
+        <v>67.5</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>77.5</v>
+        <v>337.5</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -4526,28 +4546,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n">
-        <v>60</v>
+      <c r="D106" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F106" s="10" t="n">
-        <v>480</v>
+        <v>7</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>472.5</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>72</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -4555,28 +4575,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D107" s="8" t="n">
-        <v>20</v>
+      <c r="D107" s="9" t="n">
+        <v>67.5</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F107" s="8" t="n">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>25</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
@@ -4584,28 +4604,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n">
-        <v>40</v>
+      <c r="D108" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F108" s="10" t="n">
-        <v>400</v>
+        <v>3</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>202.5</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>50</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -4613,28 +4633,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n">
-        <v>50</v>
+      <c r="D109" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F109" s="8" t="n">
-        <v>250</v>
+        <v>1</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>56.2</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -4643,16 +4663,16 @@
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>195</v>
+        <v>480</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111">
@@ -4672,16 +4692,16 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>520</v>
+        <v>200</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112">
@@ -4701,16 +4721,16 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>76.40000000000001</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
@@ -4730,16 +4750,16 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>69.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="114">
@@ -4762,13 +4782,13 @@
         <v>65</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>325</v>
+        <v>195</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -4791,13 +4811,13 @@
         <v>65</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>325</v>
+        <v>520</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>78</v>
       </c>
     </row>
     <row r="116">
@@ -4817,22 +4837,22 @@
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>75</v>
+        <v>455</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>76.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -4846,22 +4866,22 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>35</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -4875,22 +4895,22 @@
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>50</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
@@ -4904,22 +4924,22 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>53.8</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -4932,17 +4952,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D120" s="11" t="n">
-        <v>62.5</v>
+      <c r="D120" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F120" s="11" t="n">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -4961,17 +4981,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D121" s="9" t="n">
-        <v>62.5</v>
+      <c r="D121" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>437.5</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>280</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>73.40000000000001</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122">
@@ -4990,17 +5010,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D122" s="11" t="n">
-        <v>62.5</v>
+      <c r="D122" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F122" s="11" t="n">
-        <v>500</v>
+        <v>10</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>400</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
@@ -5019,17 +5039,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D123" s="9" t="n">
-        <v>62.5</v>
+      <c r="D123" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F123" s="9" t="n">
-        <v>500</v>
+        <v>3</v>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>150</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>75</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="124">
@@ -5052,13 +5072,13 @@
         <v>62.5</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>187.5</v>
+        <v>500</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>67.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125">
@@ -5078,248 +5098,248 @@
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>72.2</v>
+        <v>62.5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>72.2</v>
+        <v>437.5</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="n">
-        <v>10</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F126" s="10" t="n">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>500</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="n">
-        <v>20</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F127" s="8" t="n">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>500</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>22.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="n">
-        <v>40</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>187.5</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>45</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="n">
-        <v>50</v>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F129" s="8" t="n">
-        <v>150</v>
+        <v>1</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>72.2</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>53.8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E130" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>48</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E132" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>56.2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="134">
@@ -5339,16 +5359,16 @@
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135">
@@ -5368,16 +5388,16 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="136">
@@ -5397,16 +5417,16 @@
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>480</v>
+        <v>250</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>72</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="137">
@@ -5426,16 +5446,16 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="138">
@@ -5455,22 +5475,22 @@
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -5484,22 +5504,22 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -5513,22 +5533,22 @@
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E140" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -5542,22 +5562,22 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>56.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -5571,27 +5591,27 @@
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>66</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
@@ -5615,12 +5635,12 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
@@ -5629,27 +5649,27 @@
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>56.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
@@ -5657,28 +5677,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D145" s="9" t="n">
-        <v>57.5</v>
+      <c r="D145" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F145" s="9" t="n">
-        <v>345</v>
+        <v>5</v>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
@@ -5686,17 +5706,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D146" s="11" t="n">
-        <v>57.5</v>
+      <c r="D146" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F146" s="11" t="n">
-        <v>460</v>
+        <v>4</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>240</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="147">
@@ -5715,17 +5735,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D147" s="9" t="n">
-        <v>57.5</v>
+      <c r="D147" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F147" s="9" t="n">
-        <v>345</v>
+        <v>10</v>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148">
@@ -5744,23 +5764,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D148" s="11" t="n">
-        <v>67.5</v>
+      <c r="D148" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F148" s="11" t="n">
-        <v>135</v>
+        <v>5</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>250</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>70.90000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -5773,23 +5793,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D149" s="8" t="n">
-        <v>20</v>
+      <c r="D149" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F149" s="8" t="n">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="F149" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>25</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -5802,23 +5822,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D150" s="10" t="n">
-        <v>40</v>
+      <c r="D150" s="11" t="n">
+        <v>57.5</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F150" s="10" t="n">
-        <v>240</v>
+        <v>8</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>460</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -5831,23 +5851,23 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D151" s="8" t="n">
-        <v>50</v>
+      <c r="D151" s="9" t="n">
+        <v>57.5</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F151" s="8" t="n">
-        <v>150</v>
+        <v>6</v>
+      </c>
+      <c r="F151" s="9" t="n">
+        <v>345</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>53.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -5860,17 +5880,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n">
-        <v>55</v>
+      <c r="D152" s="11" t="n">
+        <v>67.5</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F152" s="10" t="n">
-        <v>440</v>
+        <v>2</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>135</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>66</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -5890,16 +5910,16 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154">
@@ -5919,16 +5939,16 @@
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>61.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155">
@@ -5948,132 +5968,132 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="G156" s="11" t="n">
-        <v>11.2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E158" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>45</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Smith Machine)</t>
+          <t>Bench Press (Barbell)</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>60</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -6093,16 +6113,16 @@
         </is>
       </c>
       <c r="D160" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F160" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E160" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F160" s="10" t="n">
-        <v>400</v>
-      </c>
       <c r="G160" s="11" t="n">
-        <v>60</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="161">
@@ -6122,16 +6142,16 @@
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E161" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162">
@@ -6151,16 +6171,16 @@
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>62.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163">
@@ -6180,16 +6200,16 @@
         </is>
       </c>
       <c r="D163" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F163" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G163" s="9" t="n">
         <v>60</v>
-      </c>
-      <c r="E163" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F163" s="8" t="n">
-        <v>360</v>
-      </c>
-      <c r="G163" s="9" t="n">
-        <v>69</v>
       </c>
     </row>
     <row r="164">
@@ -6209,16 +6229,16 @@
         </is>
       </c>
       <c r="D164" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F164" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G164" s="11" t="n">
         <v>60</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F164" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G164" s="11" t="n">
-        <v>67.5</v>
       </c>
     </row>
     <row r="165">
@@ -6238,22 +6258,22 @@
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E165" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
@@ -6263,26 +6283,26 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E166" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G166" s="11" t="n">
-        <v>25</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -6292,26 +6312,26 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G167" s="9" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
@@ -6321,26 +6341,26 @@
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
+          <t>Bench Press (Smith Machine)</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G168" s="11" t="n">
-        <v>53.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -6350,20 +6370,20 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Bench Press (Barbell)</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="n">
-        <v>52.5</v>
+          <t>Bench Press (Smith Machine)</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F169" s="9" t="n">
-        <v>315</v>
+        <v>8</v>
+      </c>
+      <c r="F169" s="8" t="n">
+        <v>320</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>60.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="170">
@@ -6382,17 +6402,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D170" s="11" t="n">
-        <v>52.5</v>
+      <c r="D170" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F170" s="11" t="n">
-        <v>315</v>
+        <v>10</v>
+      </c>
+      <c r="F170" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G170" s="11" t="n">
-        <v>60.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171">
@@ -6411,17 +6431,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D171" s="9" t="n">
-        <v>52.5</v>
+      <c r="D171" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F171" s="9" t="n">
-        <v>420</v>
+        <v>6</v>
+      </c>
+      <c r="F171" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172">
@@ -6440,17 +6460,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D172" s="11" t="n">
-        <v>52.5</v>
+      <c r="D172" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F172" s="11" t="n">
-        <v>420</v>
+        <v>3</v>
+      </c>
+      <c r="F172" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="G172" s="11" t="n">
-        <v>63</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="173">
@@ -6499,27 +6519,27 @@
         </is>
       </c>
       <c r="D174" s="11" t="n">
-        <v>62.5</v>
+        <v>52.5</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>125</v>
+        <v>315</v>
       </c>
       <c r="G174" s="11" t="n">
-        <v>65.59999999999999</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
@@ -6527,28 +6547,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D175" s="8" t="n">
-        <v>20</v>
+      <c r="D175" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F175" s="8" t="n">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>420</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
@@ -6556,28 +6576,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D176" s="10" t="n">
-        <v>40</v>
+      <c r="D176" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="E176" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F176" s="10" t="n">
-        <v>320</v>
+      <c r="F176" s="11" t="n">
+        <v>420</v>
       </c>
       <c r="G176" s="11" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
@@ -6585,28 +6605,28 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D177" s="8" t="n">
-        <v>50</v>
+      <c r="D177" s="9" t="n">
+        <v>52.5</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F177" s="8" t="n">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>315</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
@@ -6614,17 +6634,17 @@
           <t>Bench Press (Barbell)</t>
         </is>
       </c>
-      <c r="D178" s="10" t="n">
-        <v>50</v>
+      <c r="D178" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F178" s="10" t="n">
-        <v>400</v>
+        <v>2</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>125</v>
       </c>
       <c r="G178" s="11" t="n">
-        <v>60</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -6644,16 +6664,16 @@
         </is>
       </c>
       <c r="D179" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>57.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="180">
@@ -6673,16 +6693,16 @@
         </is>
       </c>
       <c r="D180" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E180" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="G180" s="11" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="181">
@@ -6702,181 +6722,209 @@
         </is>
       </c>
       <c r="D181" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F181" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G181" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E181" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F181" s="8" t="n">
-        <v>180</v>
-      </c>
-      <c r="G181" s="9" t="n">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="13" t="inlineStr">
-        <is>
-          <t>週別集計</t>
-        </is>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F182" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G182" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F183" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G183" s="9" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>週</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>最大重量 (kg)</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>推定1RM (kg)</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>総Volume (kg)</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>セッション数</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F184" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G184" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="n">
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>Bench Press (Barbell)</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C185" s="9" t="n">
+      <c r="E185" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F185" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G185" s="9" t="n">
         <v>64.5</v>
       </c>
-      <c r="D185" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E185" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="10" t="inlineStr">
-        <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B186" s="11" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="C186" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="D186" s="11" t="n">
-        <v>5670</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F186" s="10" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C187" s="9" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D187" s="9" t="n">
-        <v>3545</v>
-      </c>
-      <c r="E187" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F187" s="8" t="n">
-        <v>13</v>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="13" t="inlineStr">
+        <is>
+          <t>週別集計</t>
+        </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="B188" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C188" s="11" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="D188" s="11" t="n">
-        <v>3980</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F188" s="10" t="n">
-        <v>13</v>
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>最大重量 (kg)</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>推定1RM (kg)</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>総Volume (kg)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>セッション数</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="B189" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C189" s="9" t="n">
-        <v>53.8</v>
+        <v>64.5</v>
       </c>
       <c r="D189" s="9" t="n">
-        <v>550</v>
+        <v>2200</v>
       </c>
       <c r="E189" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>2026-W17</t>
-        </is>
-      </c>
-      <c r="B190" s="10" t="n">
-        <v>75</v>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="n">
+        <v>62.5</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>5967.2</v>
+        <v>5670</v>
       </c>
       <c r="E190" s="10" t="n">
         <v>2</v>
@@ -6888,204 +6936,314 @@
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>2026-W18</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="B191" s="9" t="n">
-        <v>77.5</v>
+        <v>67.5</v>
       </c>
       <c r="C191" s="9" t="n">
-        <v>80.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D191" s="9" t="n">
-        <v>5355</v>
+        <v>3545</v>
       </c>
       <c r="E191" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>2026-W19</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="B192" s="10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>87</v>
+        <v>75.2</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>6122.5</v>
+        <v>3980</v>
       </c>
       <c r="E192" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>2026-W20</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="B193" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C193" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="D193" s="9" t="n">
-        <v>2045</v>
+        <v>550</v>
       </c>
       <c r="E193" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
         <is>
-          <t>2026-W21</t>
-        </is>
-      </c>
-      <c r="B194" s="11" t="n">
-        <v>77.5</v>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="n">
+        <v>75</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>4060</v>
+        <v>5967.2</v>
       </c>
       <c r="E194" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>2026-W22</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="n">
-        <v>80</v>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B195" s="9" t="n">
+        <v>77.5</v>
       </c>
       <c r="C195" s="9" t="n">
-        <v>86</v>
+        <v>80.5</v>
       </c>
       <c r="D195" s="9" t="n">
-        <v>1600</v>
+        <v>5355</v>
       </c>
       <c r="E195" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
         <is>
-          <t>2026-W23</t>
-        </is>
-      </c>
-      <c r="B196" s="11" t="n">
-        <v>82.5</v>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>5140</v>
+        <v>6122.5</v>
       </c>
       <c r="E196" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
         <is>
-          <t>2026-W24</t>
+          <t>2026-W20</t>
         </is>
       </c>
       <c r="B197" s="8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C197" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D197" s="9" t="n">
-        <v>1465</v>
+        <v>2045</v>
       </c>
       <c r="E197" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
         <is>
-          <t>2026-W25</t>
-        </is>
-      </c>
-      <c r="B198" s="10" t="n">
-        <v>85</v>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="n">
+        <v>77.5</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>3410</v>
+        <v>4060</v>
       </c>
       <c r="E198" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>2026-W31</t>
+          <t>2026-W22</t>
         </is>
       </c>
       <c r="B199" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C199" s="9" t="n">
-        <v>80.5</v>
+        <v>86</v>
       </c>
       <c r="D199" s="9" t="n">
-        <v>1720</v>
+        <v>1600</v>
       </c>
       <c r="E199" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F199" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D200" s="11" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" s="10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C201" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="B202" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="C202" s="11" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D202" s="11" t="n">
+        <v>3410</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" s="10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>2026-W31</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C203" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D203" s="9" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="8" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="inlineStr">
+        <is>
+          <t>2026-W35</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C204" s="11" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D204" s="11" t="n">
+        <v>722</v>
+      </c>
+      <c r="E204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A183:G183"/>
+    <mergeCell ref="A187:G187"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-08-30）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-09-06）</t>
         </is>
       </c>
     </row>
